--- a/projects/happyq/data/HappyQ_Tests.xlsx
+++ b/projects/happyq/data/HappyQ_Tests.xlsx
@@ -8529,7 +8529,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:M142"/>
+  <dimension ref="A1:M287"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -14353,9 +14353,5954 @@
         <v>local</v>
       </c>
     </row>
+    <row r="143">
+      <c r="A143" t="str">
+        <v>AUTH-E2E-001</v>
+      </c>
+      <c r="B143" t="str">
+        <v>Valid login redirects to app</v>
+      </c>
+      <c r="C143" t="str">
+        <v>Auth</v>
+      </c>
+      <c r="D143" t="str">
+        <v>Login</v>
+      </c>
+      <c r="E143" t="str">
+        <v>STANDARD</v>
+      </c>
+      <c r="F143" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="G143" t="str">
+        <v>User journey completed successfully</v>
+      </c>
+      <c r="H143" t="str">
+        <v/>
+      </c>
+      <c r="I143" t="str">
+        <v/>
+      </c>
+      <c r="J143">
+        <v>4</v>
+      </c>
+      <c r="K143" t="str">
+        <v>2026-07-10T04:31:17.085Z</v>
+      </c>
+      <c r="L143" t="str">
+        <v>Local Dev</v>
+      </c>
+      <c r="M143" t="str">
+        <v>local</v>
+      </c>
+    </row>
+    <row r="144">
+      <c r="A144" t="str">
+        <v>AUTH-E2E-002</v>
+      </c>
+      <c r="B144" t="str">
+        <v>Invalid password shows error</v>
+      </c>
+      <c r="C144" t="str">
+        <v>Auth</v>
+      </c>
+      <c r="D144" t="str">
+        <v>Login</v>
+      </c>
+      <c r="E144" t="str">
+        <v>STANDARD</v>
+      </c>
+      <c r="F144" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="G144" t="str">
+        <v>User journey completed successfully</v>
+      </c>
+      <c r="H144" t="str">
+        <v/>
+      </c>
+      <c r="I144" t="str">
+        <v/>
+      </c>
+      <c r="J144">
+        <v>1</v>
+      </c>
+      <c r="K144" t="str">
+        <v>2026-07-10T04:31:17.085Z</v>
+      </c>
+      <c r="L144" t="str">
+        <v>Local Dev</v>
+      </c>
+      <c r="M144" t="str">
+        <v>local</v>
+      </c>
+    </row>
+    <row r="145">
+      <c r="A145" t="str">
+        <v>AUTH-E2E-003</v>
+      </c>
+      <c r="B145" t="str">
+        <v>Login page accessible at /auth</v>
+      </c>
+      <c r="C145" t="str">
+        <v>Auth</v>
+      </c>
+      <c r="D145" t="str">
+        <v>Login</v>
+      </c>
+      <c r="E145" t="str">
+        <v>STANDARD</v>
+      </c>
+      <c r="F145" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="G145" t="str">
+        <v>User journey completed successfully</v>
+      </c>
+      <c r="H145" t="str">
+        <v/>
+      </c>
+      <c r="I145" t="str">
+        <v/>
+      </c>
+      <c r="J145">
+        <v>1</v>
+      </c>
+      <c r="K145" t="str">
+        <v>2026-07-10T04:31:17.085Z</v>
+      </c>
+      <c r="L145" t="str">
+        <v>Local Dev</v>
+      </c>
+      <c r="M145" t="str">
+        <v>local</v>
+      </c>
+    </row>
+    <row r="146">
+      <c r="A146" t="str">
+        <v>PAT-E2E-001</v>
+      </c>
+      <c r="B146" t="str">
+        <v>Patient list page loads</v>
+      </c>
+      <c r="C146" t="str">
+        <v>Patients</v>
+      </c>
+      <c r="D146" t="str">
+        <v>Patient List</v>
+      </c>
+      <c r="E146" t="str">
+        <v>STANDARD</v>
+      </c>
+      <c r="F146" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="G146" t="str">
+        <v>User journey completed successfully</v>
+      </c>
+      <c r="H146" t="str">
+        <v/>
+      </c>
+      <c r="I146" t="str">
+        <v/>
+      </c>
+      <c r="J146">
+        <v>2</v>
+      </c>
+      <c r="K146" t="str">
+        <v>2026-07-10T04:31:17.085Z</v>
+      </c>
+      <c r="L146" t="str">
+        <v>Local Dev</v>
+      </c>
+      <c r="M146" t="str">
+        <v>local</v>
+      </c>
+    </row>
+    <row r="147">
+      <c r="A147" t="str">
+        <v>PAT-E2E-002</v>
+      </c>
+      <c r="B147" t="str">
+        <v>Search filters patient list</v>
+      </c>
+      <c r="C147" t="str">
+        <v>Patients</v>
+      </c>
+      <c r="D147" t="str">
+        <v>Patient List</v>
+      </c>
+      <c r="E147" t="str">
+        <v>STANDARD</v>
+      </c>
+      <c r="F147" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="G147" t="str">
+        <v>User journey completed successfully</v>
+      </c>
+      <c r="H147" t="str">
+        <v/>
+      </c>
+      <c r="I147" t="str">
+        <v/>
+      </c>
+      <c r="J147">
+        <v>2</v>
+      </c>
+      <c r="K147" t="str">
+        <v>2026-07-10T04:31:17.085Z</v>
+      </c>
+      <c r="L147" t="str">
+        <v>Local Dev</v>
+      </c>
+      <c r="M147" t="str">
+        <v>local</v>
+      </c>
+    </row>
+    <row r="148">
+      <c r="A148" t="str">
+        <v>PAT-E2E-003</v>
+      </c>
+      <c r="B148" t="str">
+        <v>Add Patient dialog opens</v>
+      </c>
+      <c r="C148" t="str">
+        <v>Patients</v>
+      </c>
+      <c r="D148" t="str">
+        <v>Add Patient</v>
+      </c>
+      <c r="E148" t="str">
+        <v>STANDARD</v>
+      </c>
+      <c r="F148" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="G148" t="str">
+        <v>User journey completed successfully</v>
+      </c>
+      <c r="H148" t="str">
+        <v/>
+      </c>
+      <c r="I148" t="str">
+        <v/>
+      </c>
+      <c r="J148">
+        <v>2</v>
+      </c>
+      <c r="K148" t="str">
+        <v>2026-07-10T04:31:17.085Z</v>
+      </c>
+      <c r="L148" t="str">
+        <v>Local Dev</v>
+      </c>
+      <c r="M148" t="str">
+        <v>local</v>
+      </c>
+    </row>
+    <row r="149">
+      <c r="A149" t="str">
+        <v>PAT-E2E-004</v>
+      </c>
+      <c r="B149" t="str">
+        <v>Add new patient successfully</v>
+      </c>
+      <c r="C149" t="str">
+        <v>Patients</v>
+      </c>
+      <c r="D149" t="str">
+        <v>Add Patient</v>
+      </c>
+      <c r="E149" t="str">
+        <v>STANDARD</v>
+      </c>
+      <c r="F149" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="G149" t="str">
+        <v>User journey completed successfully</v>
+      </c>
+      <c r="H149" t="str">
+        <v/>
+      </c>
+      <c r="I149" t="str">
+        <v/>
+      </c>
+      <c r="J149">
+        <v>3</v>
+      </c>
+      <c r="K149" t="str">
+        <v>2026-07-10T04:31:17.085Z</v>
+      </c>
+      <c r="L149" t="str">
+        <v>Local Dev</v>
+      </c>
+      <c r="M149" t="str">
+        <v>local</v>
+      </c>
+    </row>
+    <row r="150">
+      <c r="A150" t="str">
+        <v>PAT-E2E-005</v>
+      </c>
+      <c r="B150" t="str">
+        <v>Add patient validation — required fields</v>
+      </c>
+      <c r="C150" t="str">
+        <v>Patients</v>
+      </c>
+      <c r="D150" t="str">
+        <v>Add Patient</v>
+      </c>
+      <c r="E150" t="str">
+        <v>STANDARD</v>
+      </c>
+      <c r="F150" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="G150" t="str">
+        <v>User journey completed successfully</v>
+      </c>
+      <c r="H150" t="str">
+        <v/>
+      </c>
+      <c r="I150" t="str">
+        <v/>
+      </c>
+      <c r="J150">
+        <v>2</v>
+      </c>
+      <c r="K150" t="str">
+        <v>2026-07-10T04:31:17.085Z</v>
+      </c>
+      <c r="L150" t="str">
+        <v>Local Dev</v>
+      </c>
+      <c r="M150" t="str">
+        <v>local</v>
+      </c>
+    </row>
+    <row r="151">
+      <c r="A151" t="str">
+        <v>PAT-E2E-006</v>
+      </c>
+      <c r="B151" t="str">
+        <v>Cancel Add Patient closes dialog</v>
+      </c>
+      <c r="C151" t="str">
+        <v>Patients</v>
+      </c>
+      <c r="D151" t="str">
+        <v>Add Patient</v>
+      </c>
+      <c r="E151" t="str">
+        <v>STANDARD</v>
+      </c>
+      <c r="F151" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="G151" t="str">
+        <v>User journey completed successfully</v>
+      </c>
+      <c r="H151" t="str">
+        <v/>
+      </c>
+      <c r="I151" t="str">
+        <v/>
+      </c>
+      <c r="J151">
+        <v>3</v>
+      </c>
+      <c r="K151" t="str">
+        <v>2026-07-10T04:31:17.085Z</v>
+      </c>
+      <c r="L151" t="str">
+        <v>Local Dev</v>
+      </c>
+      <c r="M151" t="str">
+        <v>local</v>
+      </c>
+    </row>
+    <row r="152">
+      <c r="A152" t="str">
+        <v>APT-E2E-001</v>
+      </c>
+      <c r="B152" t="str">
+        <v>Appointments calendar loads</v>
+      </c>
+      <c r="C152" t="str">
+        <v>Appointments</v>
+      </c>
+      <c r="D152" t="str">
+        <v>Calendar</v>
+      </c>
+      <c r="E152" t="str">
+        <v>RECEPTIONIST</v>
+      </c>
+      <c r="F152" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="G152" t="str">
+        <v>User journey completed successfully</v>
+      </c>
+      <c r="H152" t="str">
+        <v/>
+      </c>
+      <c r="I152" t="str">
+        <v/>
+      </c>
+      <c r="J152">
+        <v>2</v>
+      </c>
+      <c r="K152" t="str">
+        <v>2026-07-10T04:31:17.085Z</v>
+      </c>
+      <c r="L152" t="str">
+        <v>Local Dev</v>
+      </c>
+      <c r="M152" t="str">
+        <v>local</v>
+      </c>
+    </row>
+    <row r="153">
+      <c r="A153" t="str">
+        <v>APT-E2E-002</v>
+      </c>
+      <c r="B153" t="str">
+        <v>Today button navigates to current date</v>
+      </c>
+      <c r="C153" t="str">
+        <v>Appointments</v>
+      </c>
+      <c r="D153" t="str">
+        <v>Calendar</v>
+      </c>
+      <c r="E153" t="str">
+        <v>RECEPTIONIST</v>
+      </c>
+      <c r="F153" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="G153" t="str">
+        <v>User journey completed successfully</v>
+      </c>
+      <c r="H153" t="str">
+        <v/>
+      </c>
+      <c r="I153" t="str">
+        <v/>
+      </c>
+      <c r="J153">
+        <v>1</v>
+      </c>
+      <c r="K153" t="str">
+        <v>2026-07-10T04:31:17.085Z</v>
+      </c>
+      <c r="L153" t="str">
+        <v>Local Dev</v>
+      </c>
+      <c r="M153" t="str">
+        <v>local</v>
+      </c>
+    </row>
+    <row r="154">
+      <c r="A154" t="str">
+        <v>APT-E2E-003</v>
+      </c>
+      <c r="B154" t="str">
+        <v>Switch to week view</v>
+      </c>
+      <c r="C154" t="str">
+        <v>Appointments</v>
+      </c>
+      <c r="D154" t="str">
+        <v>Calendar</v>
+      </c>
+      <c r="E154" t="str">
+        <v>RECEPTIONIST</v>
+      </c>
+      <c r="F154" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="G154" t="str">
+        <v>User journey completed successfully</v>
+      </c>
+      <c r="H154" t="str">
+        <v/>
+      </c>
+      <c r="I154" t="str">
+        <v/>
+      </c>
+      <c r="J154">
+        <v>2</v>
+      </c>
+      <c r="K154" t="str">
+        <v>2026-07-10T04:31:17.085Z</v>
+      </c>
+      <c r="L154" t="str">
+        <v>Local Dev</v>
+      </c>
+      <c r="M154" t="str">
+        <v>local</v>
+      </c>
+    </row>
+    <row r="155">
+      <c r="A155" t="str">
+        <v>APT-E2E-004</v>
+      </c>
+      <c r="B155" t="str">
+        <v>Book Appointment dialog opens</v>
+      </c>
+      <c r="C155" t="str">
+        <v>Appointments</v>
+      </c>
+      <c r="D155" t="str">
+        <v>Book Appointment</v>
+      </c>
+      <c r="E155" t="str">
+        <v>RECEPTIONIST</v>
+      </c>
+      <c r="F155" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="G155" t="str">
+        <v>User journey completed successfully</v>
+      </c>
+      <c r="H155" t="str">
+        <v/>
+      </c>
+      <c r="I155" t="str">
+        <v/>
+      </c>
+      <c r="J155">
+        <v>2</v>
+      </c>
+      <c r="K155" t="str">
+        <v>2026-07-10T04:31:17.085Z</v>
+      </c>
+      <c r="L155" t="str">
+        <v>Local Dev</v>
+      </c>
+      <c r="M155" t="str">
+        <v>local</v>
+      </c>
+    </row>
+    <row r="156">
+      <c r="A156" t="str">
+        <v>APT-E2E-005</v>
+      </c>
+      <c r="B156" t="str">
+        <v>Cancel Book Appointment dialog</v>
+      </c>
+      <c r="C156" t="str">
+        <v>Appointments</v>
+      </c>
+      <c r="D156" t="str">
+        <v>Book Appointment</v>
+      </c>
+      <c r="E156" t="str">
+        <v>RECEPTIONIST</v>
+      </c>
+      <c r="F156" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="G156" t="str">
+        <v>User journey completed successfully</v>
+      </c>
+      <c r="H156" t="str">
+        <v/>
+      </c>
+      <c r="I156" t="str">
+        <v/>
+      </c>
+      <c r="J156">
+        <v>2</v>
+      </c>
+      <c r="K156" t="str">
+        <v>2026-07-10T04:31:17.085Z</v>
+      </c>
+      <c r="L156" t="str">
+        <v>Local Dev</v>
+      </c>
+      <c r="M156" t="str">
+        <v>local</v>
+      </c>
+    </row>
+    <row r="157">
+      <c r="A157" t="str">
+        <v>APT-E2E-006</v>
+      </c>
+      <c r="B157" t="str">
+        <v>Appointment history page loads</v>
+      </c>
+      <c r="C157" t="str">
+        <v>Appointments</v>
+      </c>
+      <c r="D157" t="str">
+        <v>Appointment History</v>
+      </c>
+      <c r="E157" t="str">
+        <v>RECEPTIONIST</v>
+      </c>
+      <c r="F157" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="G157" t="str">
+        <v>User journey completed successfully</v>
+      </c>
+      <c r="H157" t="str">
+        <v/>
+      </c>
+      <c r="I157" t="str">
+        <v/>
+      </c>
+      <c r="J157">
+        <v>1</v>
+      </c>
+      <c r="K157" t="str">
+        <v>2026-07-10T04:31:17.085Z</v>
+      </c>
+      <c r="L157" t="str">
+        <v>Local Dev</v>
+      </c>
+      <c r="M157" t="str">
+        <v>local</v>
+      </c>
+    </row>
+    <row r="158">
+      <c r="A158" t="str">
+        <v>APT-E2E-007</v>
+      </c>
+      <c r="B158" t="str">
+        <v>Search in appointment history</v>
+      </c>
+      <c r="C158" t="str">
+        <v>Appointments</v>
+      </c>
+      <c r="D158" t="str">
+        <v>Appointment History</v>
+      </c>
+      <c r="E158" t="str">
+        <v>RECEPTIONIST</v>
+      </c>
+      <c r="F158" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="G158" t="str">
+        <v>User journey completed successfully</v>
+      </c>
+      <c r="H158" t="str">
+        <v/>
+      </c>
+      <c r="I158" t="str">
+        <v/>
+      </c>
+      <c r="J158">
+        <v>2</v>
+      </c>
+      <c r="K158" t="str">
+        <v>2026-07-10T04:31:17.085Z</v>
+      </c>
+      <c r="L158" t="str">
+        <v>Local Dev</v>
+      </c>
+      <c r="M158" t="str">
+        <v>local</v>
+      </c>
+    </row>
+    <row r="159">
+      <c r="A159" t="str">
+        <v>APT-E2E-008</v>
+      </c>
+      <c r="B159" t="str">
+        <v>Status logs page loads</v>
+      </c>
+      <c r="C159" t="str">
+        <v>Appointments</v>
+      </c>
+      <c r="D159" t="str">
+        <v>Status Logs</v>
+      </c>
+      <c r="E159" t="str">
+        <v>RECEPTIONIST</v>
+      </c>
+      <c r="F159" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="G159" t="str">
+        <v>User journey completed successfully</v>
+      </c>
+      <c r="H159" t="str">
+        <v/>
+      </c>
+      <c r="I159" t="str">
+        <v/>
+      </c>
+      <c r="J159">
+        <v>1</v>
+      </c>
+      <c r="K159" t="str">
+        <v>2026-07-10T04:31:17.085Z</v>
+      </c>
+      <c r="L159" t="str">
+        <v>Local Dev</v>
+      </c>
+      <c r="M159" t="str">
+        <v>local</v>
+      </c>
+    </row>
+    <row r="160">
+      <c r="A160" t="str">
+        <v>REC-E2E-001</v>
+      </c>
+      <c r="B160" t="str">
+        <v>Reception page loads</v>
+      </c>
+      <c r="C160" t="str">
+        <v>Reception</v>
+      </c>
+      <c r="D160" t="str">
+        <v>Queue</v>
+      </c>
+      <c r="E160" t="str">
+        <v>RECEPTIONIST</v>
+      </c>
+      <c r="F160" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="G160" t="str">
+        <v>User journey completed successfully</v>
+      </c>
+      <c r="H160" t="str">
+        <v/>
+      </c>
+      <c r="I160" t="str">
+        <v/>
+      </c>
+      <c r="J160">
+        <v>1</v>
+      </c>
+      <c r="K160" t="str">
+        <v>2026-07-10T04:31:17.085Z</v>
+      </c>
+      <c r="L160" t="str">
+        <v>Local Dev</v>
+      </c>
+      <c r="M160" t="str">
+        <v>local</v>
+      </c>
+    </row>
+    <row r="161">
+      <c r="A161" t="str">
+        <v>REC-E2E-002</v>
+      </c>
+      <c r="B161" t="str">
+        <v>Switch to table view</v>
+      </c>
+      <c r="C161" t="str">
+        <v>Reception</v>
+      </c>
+      <c r="D161" t="str">
+        <v>Queue</v>
+      </c>
+      <c r="E161" t="str">
+        <v>RECEPTIONIST</v>
+      </c>
+      <c r="F161" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="G161" t="str">
+        <v>User journey completed successfully</v>
+      </c>
+      <c r="H161" t="str">
+        <v/>
+      </c>
+      <c r="I161" t="str">
+        <v/>
+      </c>
+      <c r="J161">
+        <v>1</v>
+      </c>
+      <c r="K161" t="str">
+        <v>2026-07-10T04:31:17.085Z</v>
+      </c>
+      <c r="L161" t="str">
+        <v>Local Dev</v>
+      </c>
+      <c r="M161" t="str">
+        <v>local</v>
+      </c>
+    </row>
+    <row r="162">
+      <c r="A162" t="str">
+        <v>REC-E2E-003</v>
+      </c>
+      <c r="B162" t="str">
+        <v>Switch to card view</v>
+      </c>
+      <c r="C162" t="str">
+        <v>Reception</v>
+      </c>
+      <c r="D162" t="str">
+        <v>Queue</v>
+      </c>
+      <c r="E162" t="str">
+        <v>RECEPTIONIST</v>
+      </c>
+      <c r="F162" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="G162" t="str">
+        <v>User journey completed successfully</v>
+      </c>
+      <c r="H162" t="str">
+        <v/>
+      </c>
+      <c r="I162" t="str">
+        <v/>
+      </c>
+      <c r="J162">
+        <v>2</v>
+      </c>
+      <c r="K162" t="str">
+        <v>2026-07-10T04:31:17.085Z</v>
+      </c>
+      <c r="L162" t="str">
+        <v>Local Dev</v>
+      </c>
+      <c r="M162" t="str">
+        <v>local</v>
+      </c>
+    </row>
+    <row r="163">
+      <c r="A163" t="str">
+        <v>REC-E2E-004</v>
+      </c>
+      <c r="B163" t="str">
+        <v>Search patient in reception</v>
+      </c>
+      <c r="C163" t="str">
+        <v>Reception</v>
+      </c>
+      <c r="D163" t="str">
+        <v>Queue</v>
+      </c>
+      <c r="E163" t="str">
+        <v>RECEPTIONIST</v>
+      </c>
+      <c r="F163" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="G163" t="str">
+        <v>User journey completed successfully</v>
+      </c>
+      <c r="H163" t="str">
+        <v/>
+      </c>
+      <c r="I163" t="str">
+        <v/>
+      </c>
+      <c r="J163">
+        <v>2</v>
+      </c>
+      <c r="K163" t="str">
+        <v>2026-07-10T04:31:17.085Z</v>
+      </c>
+      <c r="L163" t="str">
+        <v>Local Dev</v>
+      </c>
+      <c r="M163" t="str">
+        <v>local</v>
+      </c>
+    </row>
+    <row r="164">
+      <c r="A164" t="str">
+        <v>RBA-REC-001</v>
+      </c>
+      <c r="B164" t="str">
+        <v>Accountant cannot access reception</v>
+      </c>
+      <c r="C164" t="str">
+        <v>Reception</v>
+      </c>
+      <c r="D164" t="str">
+        <v>Queue</v>
+      </c>
+      <c r="E164" t="str">
+        <v>ACCOUNTANT</v>
+      </c>
+      <c r="F164" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="G164" t="str">
+        <v>User journey completed successfully</v>
+      </c>
+      <c r="H164" t="str">
+        <v/>
+      </c>
+      <c r="I164" t="str">
+        <v/>
+      </c>
+      <c r="J164">
+        <v>2</v>
+      </c>
+      <c r="K164" t="str">
+        <v>2026-07-10T04:31:17.085Z</v>
+      </c>
+      <c r="L164" t="str">
+        <v>Local Dev</v>
+      </c>
+      <c r="M164" t="str">
+        <v>local</v>
+      </c>
+    </row>
+    <row r="165">
+      <c r="A165" t="str">
+        <v>BIL-E2E-001</v>
+      </c>
+      <c r="B165" t="str">
+        <v>Billing dashboard loads</v>
+      </c>
+      <c r="C165" t="str">
+        <v>Billing</v>
+      </c>
+      <c r="D165" t="str">
+        <v>Dashboard</v>
+      </c>
+      <c r="E165" t="str">
+        <v>ACCOUNTANT</v>
+      </c>
+      <c r="F165" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="G165" t="str">
+        <v>User journey completed successfully</v>
+      </c>
+      <c r="H165" t="str">
+        <v/>
+      </c>
+      <c r="I165" t="str">
+        <v/>
+      </c>
+      <c r="J165">
+        <v>1</v>
+      </c>
+      <c r="K165" t="str">
+        <v>2026-07-10T04:31:17.085Z</v>
+      </c>
+      <c r="L165" t="str">
+        <v>Local Dev</v>
+      </c>
+      <c r="M165" t="str">
+        <v>local</v>
+      </c>
+    </row>
+    <row r="166">
+      <c r="A166" t="str">
+        <v>BIL-E2E-002</v>
+      </c>
+      <c r="B166" t="str">
+        <v>Billing history page loads</v>
+      </c>
+      <c r="C166" t="str">
+        <v>Billing</v>
+      </c>
+      <c r="D166" t="str">
+        <v>History</v>
+      </c>
+      <c r="E166" t="str">
+        <v>ACCOUNTANT</v>
+      </c>
+      <c r="F166" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="G166" t="str">
+        <v>User journey completed successfully</v>
+      </c>
+      <c r="H166" t="str">
+        <v/>
+      </c>
+      <c r="I166" t="str">
+        <v/>
+      </c>
+      <c r="J166">
+        <v>1</v>
+      </c>
+      <c r="K166" t="str">
+        <v>2026-07-10T04:31:17.085Z</v>
+      </c>
+      <c r="L166" t="str">
+        <v>Local Dev</v>
+      </c>
+      <c r="M166" t="str">
+        <v>local</v>
+      </c>
+    </row>
+    <row r="167">
+      <c r="A167" t="str">
+        <v>BIL-E2E-003</v>
+      </c>
+      <c r="B167" t="str">
+        <v>Outstanding balances page loads</v>
+      </c>
+      <c r="C167" t="str">
+        <v>Billing</v>
+      </c>
+      <c r="D167" t="str">
+        <v>Outstanding</v>
+      </c>
+      <c r="E167" t="str">
+        <v>ACCOUNTANT</v>
+      </c>
+      <c r="F167" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="G167" t="str">
+        <v>User journey completed successfully</v>
+      </c>
+      <c r="H167" t="str">
+        <v/>
+      </c>
+      <c r="I167" t="str">
+        <v/>
+      </c>
+      <c r="J167">
+        <v>1</v>
+      </c>
+      <c r="K167" t="str">
+        <v>2026-07-10T04:31:17.085Z</v>
+      </c>
+      <c r="L167" t="str">
+        <v>Local Dev</v>
+      </c>
+      <c r="M167" t="str">
+        <v>local</v>
+      </c>
+    </row>
+    <row r="168">
+      <c r="A168" t="str">
+        <v>BIL-E2E-004</v>
+      </c>
+      <c r="B168" t="str">
+        <v>Filter outstanding by Contacted tab</v>
+      </c>
+      <c r="C168" t="str">
+        <v>Billing</v>
+      </c>
+      <c r="D168" t="str">
+        <v>Outstanding</v>
+      </c>
+      <c r="E168" t="str">
+        <v>ACCOUNTANT</v>
+      </c>
+      <c r="F168" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="G168" t="str">
+        <v>User journey completed successfully</v>
+      </c>
+      <c r="H168" t="str">
+        <v/>
+      </c>
+      <c r="I168" t="str">
+        <v/>
+      </c>
+      <c r="J168">
+        <v>1</v>
+      </c>
+      <c r="K168" t="str">
+        <v>2026-07-10T04:31:17.085Z</v>
+      </c>
+      <c r="L168" t="str">
+        <v>Local Dev</v>
+      </c>
+      <c r="M168" t="str">
+        <v>local</v>
+      </c>
+    </row>
+    <row r="169">
+      <c r="A169" t="str">
+        <v>BIL-E2E-005</v>
+      </c>
+      <c r="B169" t="str">
+        <v>Search in outstanding balances</v>
+      </c>
+      <c r="C169" t="str">
+        <v>Billing</v>
+      </c>
+      <c r="D169" t="str">
+        <v>Outstanding</v>
+      </c>
+      <c r="E169" t="str">
+        <v>ACCOUNTANT</v>
+      </c>
+      <c r="F169" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="G169" t="str">
+        <v>User journey completed successfully</v>
+      </c>
+      <c r="H169" t="str">
+        <v/>
+      </c>
+      <c r="I169" t="str">
+        <v/>
+      </c>
+      <c r="J169">
+        <v>2</v>
+      </c>
+      <c r="K169" t="str">
+        <v>2026-07-10T04:31:17.085Z</v>
+      </c>
+      <c r="L169" t="str">
+        <v>Local Dev</v>
+      </c>
+      <c r="M169" t="str">
+        <v>local</v>
+      </c>
+    </row>
+    <row r="170">
+      <c r="A170" t="str">
+        <v>BIL-E2E-006</v>
+      </c>
+      <c r="B170" t="str">
+        <v>Invoice reports page loads</v>
+      </c>
+      <c r="C170" t="str">
+        <v>Billing</v>
+      </c>
+      <c r="D170" t="str">
+        <v>Invoice Reports</v>
+      </c>
+      <c r="E170" t="str">
+        <v>ACCOUNTANT</v>
+      </c>
+      <c r="F170" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="G170" t="str">
+        <v>User journey completed successfully</v>
+      </c>
+      <c r="H170" t="str">
+        <v/>
+      </c>
+      <c r="I170" t="str">
+        <v/>
+      </c>
+      <c r="J170">
+        <v>2</v>
+      </c>
+      <c r="K170" t="str">
+        <v>2026-07-10T04:31:17.085Z</v>
+      </c>
+      <c r="L170" t="str">
+        <v>Local Dev</v>
+      </c>
+      <c r="M170" t="str">
+        <v>local</v>
+      </c>
+    </row>
+    <row r="171">
+      <c r="A171" t="str">
+        <v>BIL-E2E-007</v>
+      </c>
+      <c r="B171" t="str">
+        <v>Switch to audit log tab</v>
+      </c>
+      <c r="C171" t="str">
+        <v>Billing</v>
+      </c>
+      <c r="D171" t="str">
+        <v>Invoice Reports</v>
+      </c>
+      <c r="E171" t="str">
+        <v>ACCOUNTANT</v>
+      </c>
+      <c r="F171" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="G171" t="str">
+        <v>User journey completed successfully</v>
+      </c>
+      <c r="H171" t="str">
+        <v/>
+      </c>
+      <c r="I171" t="str">
+        <v/>
+      </c>
+      <c r="J171">
+        <v>1</v>
+      </c>
+      <c r="K171" t="str">
+        <v>2026-07-10T04:31:17.085Z</v>
+      </c>
+      <c r="L171" t="str">
+        <v>Local Dev</v>
+      </c>
+      <c r="M171" t="str">
+        <v>local</v>
+      </c>
+    </row>
+    <row r="172">
+      <c r="A172" t="str">
+        <v>BIL-E2E-008</v>
+      </c>
+      <c r="B172" t="str">
+        <v>Settlement dashboard loads</v>
+      </c>
+      <c r="C172" t="str">
+        <v>Billing</v>
+      </c>
+      <c r="D172" t="str">
+        <v>Settlement</v>
+      </c>
+      <c r="E172" t="str">
+        <v>ACCOUNTANT</v>
+      </c>
+      <c r="F172" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="G172" t="str">
+        <v>User journey completed successfully</v>
+      </c>
+      <c r="H172" t="str">
+        <v/>
+      </c>
+      <c r="I172" t="str">
+        <v/>
+      </c>
+      <c r="J172">
+        <v>1</v>
+      </c>
+      <c r="K172" t="str">
+        <v>2026-07-10T04:31:17.085Z</v>
+      </c>
+      <c r="L172" t="str">
+        <v>Local Dev</v>
+      </c>
+      <c r="M172" t="str">
+        <v>local</v>
+      </c>
+    </row>
+    <row r="173">
+      <c r="A173" t="str">
+        <v>BIL-E2E-009</v>
+      </c>
+      <c r="B173" t="str">
+        <v>Daily cash dashboard loads</v>
+      </c>
+      <c r="C173" t="str">
+        <v>Billing</v>
+      </c>
+      <c r="D173" t="str">
+        <v>Daily Cash</v>
+      </c>
+      <c r="E173" t="str">
+        <v>ACCOUNTANT</v>
+      </c>
+      <c r="F173" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="G173" t="str">
+        <v>User journey completed successfully</v>
+      </c>
+      <c r="H173" t="str">
+        <v/>
+      </c>
+      <c r="I173" t="str">
+        <v/>
+      </c>
+      <c r="J173">
+        <v>2</v>
+      </c>
+      <c r="K173" t="str">
+        <v>2026-07-10T04:31:17.085Z</v>
+      </c>
+      <c r="L173" t="str">
+        <v>Local Dev</v>
+      </c>
+      <c r="M173" t="str">
+        <v>local</v>
+      </c>
+    </row>
+    <row r="174">
+      <c r="A174" t="str">
+        <v>RBA-BIL-001</v>
+      </c>
+      <c r="B174" t="str">
+        <v>Doctor cannot access billing</v>
+      </c>
+      <c r="C174" t="str">
+        <v>Billing</v>
+      </c>
+      <c r="D174" t="str">
+        <v>Dashboard</v>
+      </c>
+      <c r="E174" t="str">
+        <v>DOCTOR</v>
+      </c>
+      <c r="F174" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="G174" t="str">
+        <v>User journey completed successfully</v>
+      </c>
+      <c r="H174" t="str">
+        <v/>
+      </c>
+      <c r="I174" t="str">
+        <v/>
+      </c>
+      <c r="J174">
+        <v>1</v>
+      </c>
+      <c r="K174" t="str">
+        <v>2026-07-10T04:31:17.085Z</v>
+      </c>
+      <c r="L174" t="str">
+        <v>Local Dev</v>
+      </c>
+      <c r="M174" t="str">
+        <v>local</v>
+      </c>
+    </row>
+    <row r="175">
+      <c r="A175" t="str">
+        <v>RBA-BIL-002</v>
+      </c>
+      <c r="B175" t="str">
+        <v>Receptionist cannot access billing</v>
+      </c>
+      <c r="C175" t="str">
+        <v>Billing</v>
+      </c>
+      <c r="D175" t="str">
+        <v>Dashboard</v>
+      </c>
+      <c r="E175" t="str">
+        <v>RECEPTIONIST</v>
+      </c>
+      <c r="F175" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="G175" t="str">
+        <v>User journey completed successfully</v>
+      </c>
+      <c r="H175" t="str">
+        <v/>
+      </c>
+      <c r="I175" t="str">
+        <v/>
+      </c>
+      <c r="J175">
+        <v>2</v>
+      </c>
+      <c r="K175" t="str">
+        <v>2026-07-10T04:31:17.085Z</v>
+      </c>
+      <c r="L175" t="str">
+        <v>Local Dev</v>
+      </c>
+      <c r="M175" t="str">
+        <v>local</v>
+      </c>
+    </row>
+    <row r="176">
+      <c r="A176" t="str">
+        <v>FOL-E2E-001</v>
+      </c>
+      <c r="B176" t="str">
+        <v>Follow-up dashboard loads</v>
+      </c>
+      <c r="C176" t="str">
+        <v>Follow-Ups</v>
+      </c>
+      <c r="D176" t="str">
+        <v>Dashboard</v>
+      </c>
+      <c r="E176" t="str">
+        <v>STANDARD</v>
+      </c>
+      <c r="F176" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="G176" t="str">
+        <v>User journey completed successfully</v>
+      </c>
+      <c r="H176" t="str">
+        <v/>
+      </c>
+      <c r="I176" t="str">
+        <v/>
+      </c>
+      <c r="J176">
+        <v>1</v>
+      </c>
+      <c r="K176" t="str">
+        <v>2026-07-10T04:31:17.085Z</v>
+      </c>
+      <c r="L176" t="str">
+        <v>Local Dev</v>
+      </c>
+      <c r="M176" t="str">
+        <v>local</v>
+      </c>
+    </row>
+    <row r="177">
+      <c r="A177" t="str">
+        <v>FOL-E2E-002</v>
+      </c>
+      <c r="B177" t="str">
+        <v>Stat cards are visible</v>
+      </c>
+      <c r="C177" t="str">
+        <v>Follow-Ups</v>
+      </c>
+      <c r="D177" t="str">
+        <v>Dashboard</v>
+      </c>
+      <c r="E177" t="str">
+        <v>STANDARD</v>
+      </c>
+      <c r="F177" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="G177" t="str">
+        <v>User journey completed successfully</v>
+      </c>
+      <c r="H177" t="str">
+        <v/>
+      </c>
+      <c r="I177" t="str">
+        <v/>
+      </c>
+      <c r="J177">
+        <v>2</v>
+      </c>
+      <c r="K177" t="str">
+        <v>2026-07-10T04:31:17.085Z</v>
+      </c>
+      <c r="L177" t="str">
+        <v>Local Dev</v>
+      </c>
+      <c r="M177" t="str">
+        <v>local</v>
+      </c>
+    </row>
+    <row r="178">
+      <c r="A178" t="str">
+        <v>FOL-E2E-003</v>
+      </c>
+      <c r="B178" t="str">
+        <v>Filter by Scheduled tab</v>
+      </c>
+      <c r="C178" t="str">
+        <v>Follow-Ups</v>
+      </c>
+      <c r="D178" t="str">
+        <v>Dashboard</v>
+      </c>
+      <c r="E178" t="str">
+        <v>STANDARD</v>
+      </c>
+      <c r="F178" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="G178" t="str">
+        <v>User journey completed successfully</v>
+      </c>
+      <c r="H178" t="str">
+        <v/>
+      </c>
+      <c r="I178" t="str">
+        <v/>
+      </c>
+      <c r="J178">
+        <v>1</v>
+      </c>
+      <c r="K178" t="str">
+        <v>2026-07-10T04:31:17.085Z</v>
+      </c>
+      <c r="L178" t="str">
+        <v>Local Dev</v>
+      </c>
+      <c r="M178" t="str">
+        <v>local</v>
+      </c>
+    </row>
+    <row r="179">
+      <c r="A179" t="str">
+        <v>FOL-E2E-004</v>
+      </c>
+      <c r="B179" t="str">
+        <v>Filter by Completed tab</v>
+      </c>
+      <c r="C179" t="str">
+        <v>Follow-Ups</v>
+      </c>
+      <c r="D179" t="str">
+        <v>Dashboard</v>
+      </c>
+      <c r="E179" t="str">
+        <v>STANDARD</v>
+      </c>
+      <c r="F179" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="G179" t="str">
+        <v>User journey completed successfully</v>
+      </c>
+      <c r="H179" t="str">
+        <v/>
+      </c>
+      <c r="I179" t="str">
+        <v/>
+      </c>
+      <c r="J179">
+        <v>2</v>
+      </c>
+      <c r="K179" t="str">
+        <v>2026-07-10T04:31:17.085Z</v>
+      </c>
+      <c r="L179" t="str">
+        <v>Local Dev</v>
+      </c>
+      <c r="M179" t="str">
+        <v>local</v>
+      </c>
+    </row>
+    <row r="180">
+      <c r="A180" t="str">
+        <v>TSK-E2E-001</v>
+      </c>
+      <c r="B180" t="str">
+        <v>Tasks dashboard loads</v>
+      </c>
+      <c r="C180" t="str">
+        <v>Tasks</v>
+      </c>
+      <c r="D180" t="str">
+        <v>Dashboard</v>
+      </c>
+      <c r="E180" t="str">
+        <v>STANDARD</v>
+      </c>
+      <c r="F180" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="G180" t="str">
+        <v>User journey completed successfully</v>
+      </c>
+      <c r="H180" t="str">
+        <v/>
+      </c>
+      <c r="I180" t="str">
+        <v/>
+      </c>
+      <c r="J180">
+        <v>2</v>
+      </c>
+      <c r="K180" t="str">
+        <v>2026-07-10T04:31:17.085Z</v>
+      </c>
+      <c r="L180" t="str">
+        <v>Local Dev</v>
+      </c>
+      <c r="M180" t="str">
+        <v>local</v>
+      </c>
+    </row>
+    <row r="181">
+      <c r="A181" t="str">
+        <v>DOC-E2E-001</v>
+      </c>
+      <c r="B181" t="str">
+        <v>Documents page loads</v>
+      </c>
+      <c r="C181" t="str">
+        <v>Documents</v>
+      </c>
+      <c r="D181" t="str">
+        <v>Document List</v>
+      </c>
+      <c r="E181" t="str">
+        <v>STANDARD</v>
+      </c>
+      <c r="F181" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="G181" t="str">
+        <v>User journey completed successfully</v>
+      </c>
+      <c r="H181" t="str">
+        <v/>
+      </c>
+      <c r="I181" t="str">
+        <v/>
+      </c>
+      <c r="J181">
+        <v>7305</v>
+      </c>
+      <c r="K181" t="str">
+        <v>2026-07-10T04:31:17.085Z</v>
+      </c>
+      <c r="L181" t="str">
+        <v>Local Dev</v>
+      </c>
+      <c r="M181" t="str">
+        <v>local</v>
+      </c>
+    </row>
+    <row r="182">
+      <c r="A182" t="str">
+        <v>DOC-E2E-002</v>
+      </c>
+      <c r="B182" t="str">
+        <v>Expiry tracker page loads</v>
+      </c>
+      <c r="C182" t="str">
+        <v>Documents</v>
+      </c>
+      <c r="D182" t="str">
+        <v>Expiry Tracker</v>
+      </c>
+      <c r="E182" t="str">
+        <v>STANDARD</v>
+      </c>
+      <c r="F182" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="G182" t="str">
+        <v>User journey completed successfully</v>
+      </c>
+      <c r="H182" t="str">
+        <v/>
+      </c>
+      <c r="I182" t="str">
+        <v/>
+      </c>
+      <c r="J182">
+        <v>9243</v>
+      </c>
+      <c r="K182" t="str">
+        <v>2026-07-10T04:31:17.085Z</v>
+      </c>
+      <c r="L182" t="str">
+        <v>Local Dev</v>
+      </c>
+      <c r="M182" t="str">
+        <v>local</v>
+      </c>
+    </row>
+    <row r="183">
+      <c r="A183" t="str">
+        <v>DOC-E2E-003</v>
+      </c>
+      <c r="B183" t="str">
+        <v>Filter expiry tracker by Document type</v>
+      </c>
+      <c r="C183" t="str">
+        <v>Documents</v>
+      </c>
+      <c r="D183" t="str">
+        <v>Expiry Tracker</v>
+      </c>
+      <c r="E183" t="str">
+        <v>STANDARD</v>
+      </c>
+      <c r="F183" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="G183" t="str">
+        <v>User journey completed successfully</v>
+      </c>
+      <c r="H183" t="str">
+        <v/>
+      </c>
+      <c r="I183" t="str">
+        <v/>
+      </c>
+      <c r="J183">
+        <v>3071</v>
+      </c>
+      <c r="K183" t="str">
+        <v>2026-07-10T04:31:17.085Z</v>
+      </c>
+      <c r="L183" t="str">
+        <v>Local Dev</v>
+      </c>
+      <c r="M183" t="str">
+        <v>local</v>
+      </c>
+    </row>
+    <row r="184">
+      <c r="A184" t="str">
+        <v>DOC-E2E-004</v>
+      </c>
+      <c r="B184" t="str">
+        <v>Filter expiry tracker by Equipment type</v>
+      </c>
+      <c r="C184" t="str">
+        <v>Documents</v>
+      </c>
+      <c r="D184" t="str">
+        <v>Expiry Tracker</v>
+      </c>
+      <c r="E184" t="str">
+        <v>STANDARD</v>
+      </c>
+      <c r="F184" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="G184" t="str">
+        <v>User journey completed successfully</v>
+      </c>
+      <c r="H184" t="str">
+        <v/>
+      </c>
+      <c r="I184" t="str">
+        <v/>
+      </c>
+      <c r="J184">
+        <v>11731</v>
+      </c>
+      <c r="K184" t="str">
+        <v>2026-07-10T04:31:17.085Z</v>
+      </c>
+      <c r="L184" t="str">
+        <v>Local Dev</v>
+      </c>
+      <c r="M184" t="str">
+        <v>local</v>
+      </c>
+    </row>
+    <row r="185">
+      <c r="A185" t="str">
+        <v>DOC-E2E-005</v>
+      </c>
+      <c r="B185" t="str">
+        <v>Document reports page loads</v>
+      </c>
+      <c r="C185" t="str">
+        <v>Documents</v>
+      </c>
+      <c r="D185" t="str">
+        <v>Reports</v>
+      </c>
+      <c r="E185" t="str">
+        <v>STANDARD</v>
+      </c>
+      <c r="F185" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="G185" t="str">
+        <v>User journey completed successfully</v>
+      </c>
+      <c r="H185" t="str">
+        <v/>
+      </c>
+      <c r="I185" t="str">
+        <v/>
+      </c>
+      <c r="J185">
+        <v>10286</v>
+      </c>
+      <c r="K185" t="str">
+        <v>2026-07-10T04:31:17.085Z</v>
+      </c>
+      <c r="L185" t="str">
+        <v>Local Dev</v>
+      </c>
+      <c r="M185" t="str">
+        <v>local</v>
+      </c>
+    </row>
+    <row r="186">
+      <c r="A186" t="str">
+        <v>DOC-E2E-006</v>
+      </c>
+      <c r="B186" t="str">
+        <v>Switch to audit log tab</v>
+      </c>
+      <c r="C186" t="str">
+        <v>Documents</v>
+      </c>
+      <c r="D186" t="str">
+        <v>Reports</v>
+      </c>
+      <c r="E186" t="str">
+        <v>STANDARD</v>
+      </c>
+      <c r="F186" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="G186" t="str">
+        <v>User journey completed successfully</v>
+      </c>
+      <c r="H186" t="str">
+        <v/>
+      </c>
+      <c r="I186" t="str">
+        <v/>
+      </c>
+      <c r="J186">
+        <v>1</v>
+      </c>
+      <c r="K186" t="str">
+        <v>2026-07-10T04:31:17.085Z</v>
+      </c>
+      <c r="L186" t="str">
+        <v>Local Dev</v>
+      </c>
+      <c r="M186" t="str">
+        <v>local</v>
+      </c>
+    </row>
+    <row r="187">
+      <c r="A187" t="str">
+        <v>SET-E2E-001</v>
+      </c>
+      <c r="B187" t="str">
+        <v>Locations settings page loads</v>
+      </c>
+      <c r="C187" t="str">
+        <v>Settings</v>
+      </c>
+      <c r="D187" t="str">
+        <v>Locations</v>
+      </c>
+      <c r="E187" t="str">
+        <v>STANDARD</v>
+      </c>
+      <c r="F187" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="G187" t="str">
+        <v>User journey completed successfully</v>
+      </c>
+      <c r="H187" t="str">
+        <v/>
+      </c>
+      <c r="I187" t="str">
+        <v/>
+      </c>
+      <c r="J187">
+        <v>2</v>
+      </c>
+      <c r="K187" t="str">
+        <v>2026-07-10T04:31:17.085Z</v>
+      </c>
+      <c r="L187" t="str">
+        <v>Local Dev</v>
+      </c>
+      <c r="M187" t="str">
+        <v>local</v>
+      </c>
+    </row>
+    <row r="188">
+      <c r="A188" t="str">
+        <v>SET-E2E-002</v>
+      </c>
+      <c r="B188" t="str">
+        <v>Users settings page loads</v>
+      </c>
+      <c r="C188" t="str">
+        <v>Settings</v>
+      </c>
+      <c r="D188" t="str">
+        <v>Users</v>
+      </c>
+      <c r="E188" t="str">
+        <v>STANDARD</v>
+      </c>
+      <c r="F188" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="G188" t="str">
+        <v>User journey completed successfully</v>
+      </c>
+      <c r="H188" t="str">
+        <v/>
+      </c>
+      <c r="I188" t="str">
+        <v/>
+      </c>
+      <c r="J188">
+        <v>2</v>
+      </c>
+      <c r="K188" t="str">
+        <v>2026-07-10T04:31:17.085Z</v>
+      </c>
+      <c r="L188" t="str">
+        <v>Local Dev</v>
+      </c>
+      <c r="M188" t="str">
+        <v>local</v>
+      </c>
+    </row>
+    <row r="189">
+      <c r="A189" t="str">
+        <v>SET-E2E-003</v>
+      </c>
+      <c r="B189" t="str">
+        <v>New User dialog opens</v>
+      </c>
+      <c r="C189" t="str">
+        <v>Settings</v>
+      </c>
+      <c r="D189" t="str">
+        <v>Users</v>
+      </c>
+      <c r="E189" t="str">
+        <v>STANDARD</v>
+      </c>
+      <c r="F189" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="G189" t="str">
+        <v>User journey completed successfully</v>
+      </c>
+      <c r="H189" t="str">
+        <v/>
+      </c>
+      <c r="I189" t="str">
+        <v/>
+      </c>
+      <c r="J189">
+        <v>1</v>
+      </c>
+      <c r="K189" t="str">
+        <v>2026-07-10T04:31:17.085Z</v>
+      </c>
+      <c r="L189" t="str">
+        <v>Local Dev</v>
+      </c>
+      <c r="M189" t="str">
+        <v>local</v>
+      </c>
+    </row>
+    <row r="190">
+      <c r="A190" t="str">
+        <v>SET-E2E-004</v>
+      </c>
+      <c r="B190" t="str">
+        <v>Permissions page loads with matrix</v>
+      </c>
+      <c r="C190" t="str">
+        <v>Settings</v>
+      </c>
+      <c r="D190" t="str">
+        <v>Permissions</v>
+      </c>
+      <c r="E190" t="str">
+        <v>STANDARD</v>
+      </c>
+      <c r="F190" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="G190" t="str">
+        <v>User journey completed successfully</v>
+      </c>
+      <c r="H190" t="str">
+        <v/>
+      </c>
+      <c r="I190" t="str">
+        <v/>
+      </c>
+      <c r="J190">
+        <v>1</v>
+      </c>
+      <c r="K190" t="str">
+        <v>2026-07-10T04:31:17.085Z</v>
+      </c>
+      <c r="L190" t="str">
+        <v>Local Dev</v>
+      </c>
+      <c r="M190" t="str">
+        <v>local</v>
+      </c>
+    </row>
+    <row r="191">
+      <c r="A191" t="str">
+        <v>SET-E2E-005</v>
+      </c>
+      <c r="B191" t="str">
+        <v>Services settings page loads</v>
+      </c>
+      <c r="C191" t="str">
+        <v>Settings</v>
+      </c>
+      <c r="D191" t="str">
+        <v>Services</v>
+      </c>
+      <c r="E191" t="str">
+        <v>STANDARD</v>
+      </c>
+      <c r="F191" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="G191" t="str">
+        <v>User journey completed successfully</v>
+      </c>
+      <c r="H191" t="str">
+        <v/>
+      </c>
+      <c r="I191" t="str">
+        <v/>
+      </c>
+      <c r="J191">
+        <v>1</v>
+      </c>
+      <c r="K191" t="str">
+        <v>2026-07-10T04:31:17.085Z</v>
+      </c>
+      <c r="L191" t="str">
+        <v>Local Dev</v>
+      </c>
+      <c r="M191" t="str">
+        <v>local</v>
+      </c>
+    </row>
+    <row r="192">
+      <c r="A192" t="str">
+        <v>SET-E2E-006</v>
+      </c>
+      <c r="B192" t="str">
+        <v>Queues settings page loads</v>
+      </c>
+      <c r="C192" t="str">
+        <v>Settings</v>
+      </c>
+      <c r="D192" t="str">
+        <v>Queues</v>
+      </c>
+      <c r="E192" t="str">
+        <v>STANDARD</v>
+      </c>
+      <c r="F192" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="G192" t="str">
+        <v>User journey completed successfully</v>
+      </c>
+      <c r="H192" t="str">
+        <v/>
+      </c>
+      <c r="I192" t="str">
+        <v/>
+      </c>
+      <c r="J192">
+        <v>1</v>
+      </c>
+      <c r="K192" t="str">
+        <v>2026-07-10T04:31:17.085Z</v>
+      </c>
+      <c r="L192" t="str">
+        <v>Local Dev</v>
+      </c>
+      <c r="M192" t="str">
+        <v>local</v>
+      </c>
+    </row>
+    <row r="193">
+      <c r="A193" t="str">
+        <v>RBA-SET-001</v>
+      </c>
+      <c r="B193" t="str">
+        <v>Receptionist cannot access user settings</v>
+      </c>
+      <c r="C193" t="str">
+        <v>Settings</v>
+      </c>
+      <c r="D193" t="str">
+        <v>Users</v>
+      </c>
+      <c r="E193" t="str">
+        <v>RECEPTIONIST</v>
+      </c>
+      <c r="F193" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="G193" t="str">
+        <v>User journey completed successfully</v>
+      </c>
+      <c r="H193" t="str">
+        <v/>
+      </c>
+      <c r="I193" t="str">
+        <v/>
+      </c>
+      <c r="J193">
+        <v>1</v>
+      </c>
+      <c r="K193" t="str">
+        <v>2026-07-10T04:31:17.085Z</v>
+      </c>
+      <c r="L193" t="str">
+        <v>Local Dev</v>
+      </c>
+      <c r="M193" t="str">
+        <v>local</v>
+      </c>
+    </row>
+    <row r="194">
+      <c r="A194" t="str">
+        <v>RBA-SET-002</v>
+      </c>
+      <c r="B194" t="str">
+        <v>Doctor cannot access user settings</v>
+      </c>
+      <c r="C194" t="str">
+        <v>Settings</v>
+      </c>
+      <c r="D194" t="str">
+        <v>Users</v>
+      </c>
+      <c r="E194" t="str">
+        <v>DOCTOR</v>
+      </c>
+      <c r="F194" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="G194" t="str">
+        <v>User journey completed successfully</v>
+      </c>
+      <c r="H194" t="str">
+        <v/>
+      </c>
+      <c r="I194" t="str">
+        <v/>
+      </c>
+      <c r="J194">
+        <v>1</v>
+      </c>
+      <c r="K194" t="str">
+        <v>2026-07-10T04:31:17.085Z</v>
+      </c>
+      <c r="L194" t="str">
+        <v>Local Dev</v>
+      </c>
+      <c r="M194" t="str">
+        <v>local</v>
+      </c>
+    </row>
+    <row r="195">
+      <c r="A195" t="str">
+        <v>DASH-E2E-001</v>
+      </c>
+      <c r="B195" t="str">
+        <v>Display total number of appointment and queue</v>
+      </c>
+      <c r="C195" t="str">
+        <v>Dashboard</v>
+      </c>
+      <c r="D195" t="str">
+        <v>Dashboard</v>
+      </c>
+      <c r="E195" t="str">
+        <v>STANDARD</v>
+      </c>
+      <c r="F195" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="G195" t="str">
+        <v>User journey completed successfully</v>
+      </c>
+      <c r="H195" t="str">
+        <v/>
+      </c>
+      <c r="I195" t="str">
+        <v/>
+      </c>
+      <c r="J195">
+        <v>2</v>
+      </c>
+      <c r="K195" t="str">
+        <v>2026-07-10T04:31:17.085Z</v>
+      </c>
+      <c r="L195" t="str">
+        <v>Local Dev</v>
+      </c>
+      <c r="M195" t="str">
+        <v>local</v>
+      </c>
+    </row>
+    <row r="196">
+      <c r="A196" t="str">
+        <v>PAT-E2E-007</v>
+      </c>
+      <c r="B196" t="str">
+        <v>Add patients</v>
+      </c>
+      <c r="C196" t="str">
+        <v>Patients</v>
+      </c>
+      <c r="D196" t="str">
+        <v>Patient List</v>
+      </c>
+      <c r="E196" t="str">
+        <v>STANDARD</v>
+      </c>
+      <c r="F196" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="G196" t="str">
+        <v>User journey completed successfully</v>
+      </c>
+      <c r="H196" t="str">
+        <v/>
+      </c>
+      <c r="I196" t="str">
+        <v/>
+      </c>
+      <c r="J196">
+        <v>2</v>
+      </c>
+      <c r="K196" t="str">
+        <v>2026-07-10T04:31:17.085Z</v>
+      </c>
+      <c r="L196" t="str">
+        <v>Local Dev</v>
+      </c>
+      <c r="M196" t="str">
+        <v>local</v>
+      </c>
+    </row>
+    <row r="197">
+      <c r="A197" t="str">
+        <v>REC-E2E-005</v>
+      </c>
+      <c r="B197" t="str">
+        <v>CREATE QUEUE CARD</v>
+      </c>
+      <c r="C197" t="str">
+        <v>Reception</v>
+      </c>
+      <c r="D197" t="str">
+        <v>Queue</v>
+      </c>
+      <c r="E197" t="str">
+        <v>RECEPTIONIST</v>
+      </c>
+      <c r="F197" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="G197" t="str">
+        <v>User journey completed successfully</v>
+      </c>
+      <c r="H197" t="str">
+        <v/>
+      </c>
+      <c r="I197" t="str">
+        <v/>
+      </c>
+      <c r="J197">
+        <v>2</v>
+      </c>
+      <c r="K197" t="str">
+        <v>2026-07-10T04:31:17.085Z</v>
+      </c>
+      <c r="L197" t="str">
+        <v>Local Dev</v>
+      </c>
+      <c r="M197" t="str">
+        <v>local</v>
+      </c>
+    </row>
+    <row r="198">
+      <c r="A198" t="str">
+        <v>REC-E2E-006</v>
+      </c>
+      <c r="B198" t="str">
+        <v>EDIT QUEUE</v>
+      </c>
+      <c r="C198" t="str">
+        <v>Reception</v>
+      </c>
+      <c r="D198" t="str">
+        <v>Queue</v>
+      </c>
+      <c r="E198" t="str">
+        <v>RECEPTIONIST</v>
+      </c>
+      <c r="F198" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="G198" t="str">
+        <v>User journey completed successfully</v>
+      </c>
+      <c r="H198" t="str">
+        <v/>
+      </c>
+      <c r="I198" t="str">
+        <v/>
+      </c>
+      <c r="J198">
+        <v>1</v>
+      </c>
+      <c r="K198" t="str">
+        <v>2026-07-10T04:31:17.085Z</v>
+      </c>
+      <c r="L198" t="str">
+        <v>Local Dev</v>
+      </c>
+      <c r="M198" t="str">
+        <v>local</v>
+      </c>
+    </row>
+    <row r="199">
+      <c r="A199" t="str">
+        <v>DIS-E2E-001</v>
+      </c>
+      <c r="B199" t="str">
+        <v>Display patient details in TV mode</v>
+      </c>
+      <c r="C199" t="str">
+        <v>Display</v>
+      </c>
+      <c r="D199" t="str">
+        <v>TV Display</v>
+      </c>
+      <c r="E199" t="str">
+        <v>STANDARD</v>
+      </c>
+      <c r="F199" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="G199" t="str">
+        <v>User journey completed successfully</v>
+      </c>
+      <c r="H199" t="str">
+        <v/>
+      </c>
+      <c r="I199" t="str">
+        <v/>
+      </c>
+      <c r="J199">
+        <v>3</v>
+      </c>
+      <c r="K199" t="str">
+        <v>2026-07-10T04:31:17.085Z</v>
+      </c>
+      <c r="L199" t="str">
+        <v>Local Dev</v>
+      </c>
+      <c r="M199" t="str">
+        <v>local</v>
+      </c>
+    </row>
+    <row r="200">
+      <c r="A200" t="str">
+        <v>DIS-E2E-002</v>
+      </c>
+      <c r="B200" t="str">
+        <v>Display patient details on specific card</v>
+      </c>
+      <c r="C200" t="str">
+        <v>Display</v>
+      </c>
+      <c r="D200" t="str">
+        <v>TV Display</v>
+      </c>
+      <c r="E200" t="str">
+        <v>STANDARD</v>
+      </c>
+      <c r="F200" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="G200" t="str">
+        <v>User journey completed successfully</v>
+      </c>
+      <c r="H200" t="str">
+        <v/>
+      </c>
+      <c r="I200" t="str">
+        <v/>
+      </c>
+      <c r="J200">
+        <v>2</v>
+      </c>
+      <c r="K200" t="str">
+        <v>2026-07-10T04:31:17.085Z</v>
+      </c>
+      <c r="L200" t="str">
+        <v>Local Dev</v>
+      </c>
+      <c r="M200" t="str">
+        <v>local</v>
+      </c>
+    </row>
+    <row r="201">
+      <c r="A201" t="str">
+        <v>DIS-E2E-003</v>
+      </c>
+      <c r="B201" t="str">
+        <v>Search patients</v>
+      </c>
+      <c r="C201" t="str">
+        <v>Display</v>
+      </c>
+      <c r="D201" t="str">
+        <v>TV Display</v>
+      </c>
+      <c r="E201" t="str">
+        <v>STANDARD</v>
+      </c>
+      <c r="F201" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="G201" t="str">
+        <v>User journey completed successfully</v>
+      </c>
+      <c r="H201" t="str">
+        <v/>
+      </c>
+      <c r="I201" t="str">
+        <v/>
+      </c>
+      <c r="J201">
+        <v>8</v>
+      </c>
+      <c r="K201" t="str">
+        <v>2026-07-10T04:31:17.085Z</v>
+      </c>
+      <c r="L201" t="str">
+        <v>Local Dev</v>
+      </c>
+      <c r="M201" t="str">
+        <v>local</v>
+      </c>
+    </row>
+    <row r="202">
+      <c r="A202" t="str">
+        <v>DIS-E2E-004</v>
+      </c>
+      <c r="B202" t="str">
+        <v>Calender</v>
+      </c>
+      <c r="C202" t="str">
+        <v>Display</v>
+      </c>
+      <c r="D202" t="str">
+        <v>TV Display</v>
+      </c>
+      <c r="E202" t="str">
+        <v>STANDARD</v>
+      </c>
+      <c r="F202" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="G202" t="str">
+        <v>User journey completed successfully</v>
+      </c>
+      <c r="H202" t="str">
+        <v/>
+      </c>
+      <c r="I202" t="str">
+        <v/>
+      </c>
+      <c r="J202">
+        <v>2</v>
+      </c>
+      <c r="K202" t="str">
+        <v>2026-07-10T04:31:17.085Z</v>
+      </c>
+      <c r="L202" t="str">
+        <v>Local Dev</v>
+      </c>
+      <c r="M202" t="str">
+        <v>local</v>
+      </c>
+    </row>
+    <row r="203">
+      <c r="A203" t="str">
+        <v>APT-E2E-009</v>
+      </c>
+      <c r="B203" t="str">
+        <v>create Slot</v>
+      </c>
+      <c r="C203" t="str">
+        <v>Appointments</v>
+      </c>
+      <c r="D203" t="str">
+        <v>Calendar</v>
+      </c>
+      <c r="E203" t="str">
+        <v>RECEPTIONIST</v>
+      </c>
+      <c r="F203" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="G203" t="str">
+        <v>User journey completed successfully</v>
+      </c>
+      <c r="H203" t="str">
+        <v/>
+      </c>
+      <c r="I203" t="str">
+        <v/>
+      </c>
+      <c r="J203">
+        <v>2</v>
+      </c>
+      <c r="K203" t="str">
+        <v>2026-07-10T04:31:17.085Z</v>
+      </c>
+      <c r="L203" t="str">
+        <v>Local Dev</v>
+      </c>
+      <c r="M203" t="str">
+        <v>local</v>
+      </c>
+    </row>
+    <row r="204">
+      <c r="A204" t="str">
+        <v>APT-E2E-010</v>
+      </c>
+      <c r="B204" t="str">
+        <v>Fill Form and booked</v>
+      </c>
+      <c r="C204" t="str">
+        <v>Appointments</v>
+      </c>
+      <c r="D204" t="str">
+        <v>Calendar</v>
+      </c>
+      <c r="E204" t="str">
+        <v>RECEPTIONIST</v>
+      </c>
+      <c r="F204" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="G204" t="str">
+        <v>User journey completed successfully</v>
+      </c>
+      <c r="H204" t="str">
+        <v/>
+      </c>
+      <c r="I204" t="str">
+        <v/>
+      </c>
+      <c r="J204">
+        <v>1</v>
+      </c>
+      <c r="K204" t="str">
+        <v>2026-07-10T04:31:17.085Z</v>
+      </c>
+      <c r="L204" t="str">
+        <v>Local Dev</v>
+      </c>
+      <c r="M204" t="str">
+        <v>local</v>
+      </c>
+    </row>
+    <row r="205">
+      <c r="A205" t="str">
+        <v>APT-E2E-011</v>
+      </c>
+      <c r="B205" t="str">
+        <v>select primary location</v>
+      </c>
+      <c r="C205" t="str">
+        <v>Appointments</v>
+      </c>
+      <c r="D205" t="str">
+        <v>Calendar</v>
+      </c>
+      <c r="E205" t="str">
+        <v>RECEPTIONIST</v>
+      </c>
+      <c r="F205" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="G205" t="str">
+        <v>User journey completed successfully</v>
+      </c>
+      <c r="H205" t="str">
+        <v/>
+      </c>
+      <c r="I205" t="str">
+        <v/>
+      </c>
+      <c r="J205">
+        <v>1</v>
+      </c>
+      <c r="K205" t="str">
+        <v>2026-07-10T04:31:17.085Z</v>
+      </c>
+      <c r="L205" t="str">
+        <v>Local Dev</v>
+      </c>
+      <c r="M205" t="str">
+        <v>local</v>
+      </c>
+    </row>
+    <row r="206">
+      <c r="A206" t="str">
+        <v>APT-E2E-012</v>
+      </c>
+      <c r="B206" t="str">
+        <v>display what's app button</v>
+      </c>
+      <c r="C206" t="str">
+        <v>Appointments</v>
+      </c>
+      <c r="D206" t="str">
+        <v>Calendar</v>
+      </c>
+      <c r="E206" t="str">
+        <v>RECEPTIONIST</v>
+      </c>
+      <c r="F206" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="G206" t="str">
+        <v>User journey completed successfully</v>
+      </c>
+      <c r="H206" t="str">
+        <v/>
+      </c>
+      <c r="I206" t="str">
+        <v/>
+      </c>
+      <c r="J206">
+        <v>2</v>
+      </c>
+      <c r="K206" t="str">
+        <v>2026-07-10T04:31:17.085Z</v>
+      </c>
+      <c r="L206" t="str">
+        <v>Local Dev</v>
+      </c>
+      <c r="M206" t="str">
+        <v>local</v>
+      </c>
+    </row>
+    <row r="207">
+      <c r="A207" t="str">
+        <v>REC-E2E-007</v>
+      </c>
+      <c r="B207" t="str">
+        <v>Display patient details</v>
+      </c>
+      <c r="C207" t="str">
+        <v>Reception</v>
+      </c>
+      <c r="D207" t="str">
+        <v>Queue</v>
+      </c>
+      <c r="E207" t="str">
+        <v>RECEPTIONIST</v>
+      </c>
+      <c r="F207" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="G207" t="str">
+        <v>User journey completed successfully</v>
+      </c>
+      <c r="H207" t="str">
+        <v/>
+      </c>
+      <c r="I207" t="str">
+        <v/>
+      </c>
+      <c r="J207">
+        <v>3</v>
+      </c>
+      <c r="K207" t="str">
+        <v>2026-07-10T04:31:17.085Z</v>
+      </c>
+      <c r="L207" t="str">
+        <v>Local Dev</v>
+      </c>
+      <c r="M207" t="str">
+        <v>local</v>
+      </c>
+    </row>
+    <row r="208">
+      <c r="A208" t="str">
+        <v>REC-E2E-008</v>
+      </c>
+      <c r="B208" t="str">
+        <v>Select the queue</v>
+      </c>
+      <c r="C208" t="str">
+        <v>Reception</v>
+      </c>
+      <c r="D208" t="str">
+        <v>Queue</v>
+      </c>
+      <c r="E208" t="str">
+        <v>RECEPTIONIST</v>
+      </c>
+      <c r="F208" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="G208" t="str">
+        <v>User journey completed successfully</v>
+      </c>
+      <c r="H208" t="str">
+        <v/>
+      </c>
+      <c r="I208" t="str">
+        <v/>
+      </c>
+      <c r="J208">
+        <v>2</v>
+      </c>
+      <c r="K208" t="str">
+        <v>2026-07-10T04:31:17.085Z</v>
+      </c>
+      <c r="L208" t="str">
+        <v>Local Dev</v>
+      </c>
+      <c r="M208" t="str">
+        <v>local</v>
+      </c>
+    </row>
+    <row r="209">
+      <c r="A209" t="str">
+        <v>REC-E2E-009</v>
+      </c>
+      <c r="B209" t="str">
+        <v>Select view mode</v>
+      </c>
+      <c r="C209" t="str">
+        <v>Reception</v>
+      </c>
+      <c r="D209" t="str">
+        <v>Queue</v>
+      </c>
+      <c r="E209" t="str">
+        <v>RECEPTIONIST</v>
+      </c>
+      <c r="F209" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="G209" t="str">
+        <v>User journey completed successfully</v>
+      </c>
+      <c r="H209" t="str">
+        <v/>
+      </c>
+      <c r="I209" t="str">
+        <v/>
+      </c>
+      <c r="J209">
+        <v>2</v>
+      </c>
+      <c r="K209" t="str">
+        <v>2026-07-10T04:31:17.085Z</v>
+      </c>
+      <c r="L209" t="str">
+        <v>Local Dev</v>
+      </c>
+      <c r="M209" t="str">
+        <v>local</v>
+      </c>
+    </row>
+    <row r="210">
+      <c r="A210" t="str">
+        <v>REC-E2E-010</v>
+      </c>
+      <c r="B210" t="str">
+        <v>Bill patient</v>
+      </c>
+      <c r="C210" t="str">
+        <v>Reception</v>
+      </c>
+      <c r="D210" t="str">
+        <v>Queue</v>
+      </c>
+      <c r="E210" t="str">
+        <v>RECEPTIONIST</v>
+      </c>
+      <c r="F210" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="G210" t="str">
+        <v>User journey completed successfully</v>
+      </c>
+      <c r="H210" t="str">
+        <v/>
+      </c>
+      <c r="I210" t="str">
+        <v/>
+      </c>
+      <c r="J210">
+        <v>1</v>
+      </c>
+      <c r="K210" t="str">
+        <v>2026-07-10T04:31:17.085Z</v>
+      </c>
+      <c r="L210" t="str">
+        <v>Local Dev</v>
+      </c>
+      <c r="M210" t="str">
+        <v>local</v>
+      </c>
+    </row>
+    <row r="211">
+      <c r="A211" t="str">
+        <v>REC-E2E-011</v>
+      </c>
+      <c r="B211" t="str">
+        <v>Edit existing patient details</v>
+      </c>
+      <c r="C211" t="str">
+        <v>Reception</v>
+      </c>
+      <c r="D211" t="str">
+        <v>Queue</v>
+      </c>
+      <c r="E211" t="str">
+        <v>RECEPTIONIST</v>
+      </c>
+      <c r="F211" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="G211" t="str">
+        <v>User journey completed successfully</v>
+      </c>
+      <c r="H211" t="str">
+        <v/>
+      </c>
+      <c r="I211" t="str">
+        <v/>
+      </c>
+      <c r="J211">
+        <v>1</v>
+      </c>
+      <c r="K211" t="str">
+        <v>2026-07-10T04:31:17.085Z</v>
+      </c>
+      <c r="L211" t="str">
+        <v>Local Dev</v>
+      </c>
+      <c r="M211" t="str">
+        <v>local</v>
+      </c>
+    </row>
+    <row r="212">
+      <c r="A212" t="str">
+        <v>REC-E2E-012</v>
+      </c>
+      <c r="B212" t="str">
+        <v>Edit blank fields</v>
+      </c>
+      <c r="C212" t="str">
+        <v>Reception</v>
+      </c>
+      <c r="D212" t="str">
+        <v>Queue</v>
+      </c>
+      <c r="E212" t="str">
+        <v>RECEPTIONIST</v>
+      </c>
+      <c r="F212" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="G212" t="str">
+        <v>User journey completed successfully</v>
+      </c>
+      <c r="H212" t="str">
+        <v/>
+      </c>
+      <c r="I212" t="str">
+        <v/>
+      </c>
+      <c r="J212">
+        <v>1</v>
+      </c>
+      <c r="K212" t="str">
+        <v>2026-07-10T04:31:17.085Z</v>
+      </c>
+      <c r="L212" t="str">
+        <v>Local Dev</v>
+      </c>
+      <c r="M212" t="str">
+        <v>local</v>
+      </c>
+    </row>
+    <row r="213">
+      <c r="A213" t="str">
+        <v>REC-E2E-013</v>
+      </c>
+      <c r="B213" t="str">
+        <v>Click arrive</v>
+      </c>
+      <c r="C213" t="str">
+        <v>Reception</v>
+      </c>
+      <c r="D213" t="str">
+        <v>Queue</v>
+      </c>
+      <c r="E213" t="str">
+        <v>RECEPTIONIST</v>
+      </c>
+      <c r="F213" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="G213" t="str">
+        <v>User journey completed successfully</v>
+      </c>
+      <c r="H213" t="str">
+        <v/>
+      </c>
+      <c r="I213" t="str">
+        <v/>
+      </c>
+      <c r="J213">
+        <v>2</v>
+      </c>
+      <c r="K213" t="str">
+        <v>2026-07-10T04:31:17.085Z</v>
+      </c>
+      <c r="L213" t="str">
+        <v>Local Dev</v>
+      </c>
+      <c r="M213" t="str">
+        <v>local</v>
+      </c>
+    </row>
+    <row r="214">
+      <c r="A214" t="str">
+        <v>REC-E2E-014</v>
+      </c>
+      <c r="B214" t="str">
+        <v>Click no show</v>
+      </c>
+      <c r="C214" t="str">
+        <v>Reception</v>
+      </c>
+      <c r="D214" t="str">
+        <v>Queue</v>
+      </c>
+      <c r="E214" t="str">
+        <v>RECEPTIONIST</v>
+      </c>
+      <c r="F214" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="G214" t="str">
+        <v>User journey completed successfully</v>
+      </c>
+      <c r="H214" t="str">
+        <v/>
+      </c>
+      <c r="I214" t="str">
+        <v/>
+      </c>
+      <c r="J214">
+        <v>2</v>
+      </c>
+      <c r="K214" t="str">
+        <v>2026-07-10T04:31:17.085Z</v>
+      </c>
+      <c r="L214" t="str">
+        <v>Local Dev</v>
+      </c>
+      <c r="M214" t="str">
+        <v>local</v>
+      </c>
+    </row>
+    <row r="215">
+      <c r="A215" t="str">
+        <v>REC-E2E-015</v>
+      </c>
+      <c r="B215" t="str">
+        <v>Click wait</v>
+      </c>
+      <c r="C215" t="str">
+        <v>Reception</v>
+      </c>
+      <c r="D215" t="str">
+        <v>Queue</v>
+      </c>
+      <c r="E215" t="str">
+        <v>RECEPTIONIST</v>
+      </c>
+      <c r="F215" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="G215" t="str">
+        <v>User journey completed successfully</v>
+      </c>
+      <c r="H215" t="str">
+        <v/>
+      </c>
+      <c r="I215" t="str">
+        <v/>
+      </c>
+      <c r="J215">
+        <v>1</v>
+      </c>
+      <c r="K215" t="str">
+        <v>2026-07-10T04:31:17.085Z</v>
+      </c>
+      <c r="L215" t="str">
+        <v>Local Dev</v>
+      </c>
+      <c r="M215" t="str">
+        <v>local</v>
+      </c>
+    </row>
+    <row r="216">
+      <c r="A216" t="str">
+        <v>REC-E2E-016</v>
+      </c>
+      <c r="B216" t="str">
+        <v>Click call for scan</v>
+      </c>
+      <c r="C216" t="str">
+        <v>Reception</v>
+      </c>
+      <c r="D216" t="str">
+        <v>Queue</v>
+      </c>
+      <c r="E216" t="str">
+        <v>RECEPTIONIST</v>
+      </c>
+      <c r="F216" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="G216" t="str">
+        <v>User journey completed successfully</v>
+      </c>
+      <c r="H216" t="str">
+        <v/>
+      </c>
+      <c r="I216" t="str">
+        <v/>
+      </c>
+      <c r="J216">
+        <v>1</v>
+      </c>
+      <c r="K216" t="str">
+        <v>2026-07-10T04:31:17.085Z</v>
+      </c>
+      <c r="L216" t="str">
+        <v>Local Dev</v>
+      </c>
+      <c r="M216" t="str">
+        <v>local</v>
+      </c>
+    </row>
+    <row r="217">
+      <c r="A217" t="str">
+        <v>REC-E2E-017</v>
+      </c>
+      <c r="B217" t="str">
+        <v>Click pending</v>
+      </c>
+      <c r="C217" t="str">
+        <v>Reception</v>
+      </c>
+      <c r="D217" t="str">
+        <v>Queue</v>
+      </c>
+      <c r="E217" t="str">
+        <v>RECEPTIONIST</v>
+      </c>
+      <c r="F217" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="G217" t="str">
+        <v>User journey completed successfully</v>
+      </c>
+      <c r="H217" t="str">
+        <v/>
+      </c>
+      <c r="I217" t="str">
+        <v/>
+      </c>
+      <c r="J217">
+        <v>1</v>
+      </c>
+      <c r="K217" t="str">
+        <v>2026-07-10T04:31:17.085Z</v>
+      </c>
+      <c r="L217" t="str">
+        <v>Local Dev</v>
+      </c>
+      <c r="M217" t="str">
+        <v>local</v>
+      </c>
+    </row>
+    <row r="218">
+      <c r="A218" t="str">
+        <v>REC-E2E-018</v>
+      </c>
+      <c r="B218" t="str">
+        <v>Click consultant</v>
+      </c>
+      <c r="C218" t="str">
+        <v>Reception</v>
+      </c>
+      <c r="D218" t="str">
+        <v>Queue</v>
+      </c>
+      <c r="E218" t="str">
+        <v>RECEPTIONIST</v>
+      </c>
+      <c r="F218" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="G218" t="str">
+        <v>User journey completed successfully</v>
+      </c>
+      <c r="H218" t="str">
+        <v/>
+      </c>
+      <c r="I218" t="str">
+        <v/>
+      </c>
+      <c r="J218">
+        <v>2</v>
+      </c>
+      <c r="K218" t="str">
+        <v>2026-07-10T04:31:17.085Z</v>
+      </c>
+      <c r="L218" t="str">
+        <v>Local Dev</v>
+      </c>
+      <c r="M218" t="str">
+        <v>local</v>
+      </c>
+    </row>
+    <row r="219">
+      <c r="A219" t="str">
+        <v>REC-E2E-019</v>
+      </c>
+      <c r="B219" t="str">
+        <v>Click completed</v>
+      </c>
+      <c r="C219" t="str">
+        <v>Reception</v>
+      </c>
+      <c r="D219" t="str">
+        <v>Queue</v>
+      </c>
+      <c r="E219" t="str">
+        <v>RECEPTIONIST</v>
+      </c>
+      <c r="F219" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="G219" t="str">
+        <v>User journey completed successfully</v>
+      </c>
+      <c r="H219" t="str">
+        <v/>
+      </c>
+      <c r="I219" t="str">
+        <v/>
+      </c>
+      <c r="J219">
+        <v>1</v>
+      </c>
+      <c r="K219" t="str">
+        <v>2026-07-10T04:31:17.085Z</v>
+      </c>
+      <c r="L219" t="str">
+        <v>Local Dev</v>
+      </c>
+      <c r="M219" t="str">
+        <v>local</v>
+      </c>
+    </row>
+    <row r="220">
+      <c r="A220" t="str">
+        <v>CON-E2E-001</v>
+      </c>
+      <c r="B220" t="str">
+        <v>Display patient details</v>
+      </c>
+      <c r="C220" t="str">
+        <v>Consultant</v>
+      </c>
+      <c r="D220" t="str">
+        <v>Consultant Queue</v>
+      </c>
+      <c r="E220" t="str">
+        <v>DOCTOR</v>
+      </c>
+      <c r="F220" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="G220" t="str">
+        <v>User journey completed successfully</v>
+      </c>
+      <c r="H220" t="str">
+        <v/>
+      </c>
+      <c r="I220" t="str">
+        <v/>
+      </c>
+      <c r="J220">
+        <v>2</v>
+      </c>
+      <c r="K220" t="str">
+        <v>2026-07-10T04:31:17.085Z</v>
+      </c>
+      <c r="L220" t="str">
+        <v>Local Dev</v>
+      </c>
+      <c r="M220" t="str">
+        <v>local</v>
+      </c>
+    </row>
+    <row r="221">
+      <c r="A221" t="str">
+        <v>CON-E2E-002</v>
+      </c>
+      <c r="B221" t="str">
+        <v>Calender</v>
+      </c>
+      <c r="C221" t="str">
+        <v>Consultant</v>
+      </c>
+      <c r="D221" t="str">
+        <v>Consultant Queue</v>
+      </c>
+      <c r="E221" t="str">
+        <v>DOCTOR</v>
+      </c>
+      <c r="F221" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="G221" t="str">
+        <v>User journey completed successfully</v>
+      </c>
+      <c r="H221" t="str">
+        <v/>
+      </c>
+      <c r="I221" t="str">
+        <v/>
+      </c>
+      <c r="J221">
+        <v>1</v>
+      </c>
+      <c r="K221" t="str">
+        <v>2026-07-10T04:31:17.085Z</v>
+      </c>
+      <c r="L221" t="str">
+        <v>Local Dev</v>
+      </c>
+      <c r="M221" t="str">
+        <v>local</v>
+      </c>
+    </row>
+    <row r="222">
+      <c r="A222" t="str">
+        <v>CON-E2E-003</v>
+      </c>
+      <c r="B222" t="str">
+        <v>Select queue</v>
+      </c>
+      <c r="C222" t="str">
+        <v>Consultant</v>
+      </c>
+      <c r="D222" t="str">
+        <v>Consultant Queue</v>
+      </c>
+      <c r="E222" t="str">
+        <v>DOCTOR</v>
+      </c>
+      <c r="F222" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="G222" t="str">
+        <v>User journey completed successfully</v>
+      </c>
+      <c r="H222" t="str">
+        <v/>
+      </c>
+      <c r="I222" t="str">
+        <v/>
+      </c>
+      <c r="J222">
+        <v>2</v>
+      </c>
+      <c r="K222" t="str">
+        <v>2026-07-10T04:31:17.085Z</v>
+      </c>
+      <c r="L222" t="str">
+        <v>Local Dev</v>
+      </c>
+      <c r="M222" t="str">
+        <v>local</v>
+      </c>
+    </row>
+    <row r="223">
+      <c r="A223" t="str">
+        <v>CON-E2E-004</v>
+      </c>
+      <c r="B223" t="str">
+        <v>Click wait</v>
+      </c>
+      <c r="C223" t="str">
+        <v>Consultant</v>
+      </c>
+      <c r="D223" t="str">
+        <v>Consultant Queue</v>
+      </c>
+      <c r="E223" t="str">
+        <v>DOCTOR</v>
+      </c>
+      <c r="F223" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="G223" t="str">
+        <v>User journey completed successfully</v>
+      </c>
+      <c r="H223" t="str">
+        <v/>
+      </c>
+      <c r="I223" t="str">
+        <v/>
+      </c>
+      <c r="J223">
+        <v>1</v>
+      </c>
+      <c r="K223" t="str">
+        <v>2026-07-10T04:31:17.085Z</v>
+      </c>
+      <c r="L223" t="str">
+        <v>Local Dev</v>
+      </c>
+      <c r="M223" t="str">
+        <v>local</v>
+      </c>
+    </row>
+    <row r="224">
+      <c r="A224" t="str">
+        <v>CON-E2E-005</v>
+      </c>
+      <c r="B224" t="str">
+        <v>Click call for scan</v>
+      </c>
+      <c r="C224" t="str">
+        <v>Consultant</v>
+      </c>
+      <c r="D224" t="str">
+        <v>Consultant Queue</v>
+      </c>
+      <c r="E224" t="str">
+        <v>DOCTOR</v>
+      </c>
+      <c r="F224" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="G224" t="str">
+        <v>User journey completed successfully</v>
+      </c>
+      <c r="H224" t="str">
+        <v/>
+      </c>
+      <c r="I224" t="str">
+        <v/>
+      </c>
+      <c r="J224">
+        <v>1</v>
+      </c>
+      <c r="K224" t="str">
+        <v>2026-07-10T04:31:17.085Z</v>
+      </c>
+      <c r="L224" t="str">
+        <v>Local Dev</v>
+      </c>
+      <c r="M224" t="str">
+        <v>local</v>
+      </c>
+    </row>
+    <row r="225">
+      <c r="A225" t="str">
+        <v>CON-E2E-006</v>
+      </c>
+      <c r="B225" t="str">
+        <v>Click pending</v>
+      </c>
+      <c r="C225" t="str">
+        <v>Consultant</v>
+      </c>
+      <c r="D225" t="str">
+        <v>Consultant Queue</v>
+      </c>
+      <c r="E225" t="str">
+        <v>DOCTOR</v>
+      </c>
+      <c r="F225" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="G225" t="str">
+        <v>User journey completed successfully</v>
+      </c>
+      <c r="H225" t="str">
+        <v/>
+      </c>
+      <c r="I225" t="str">
+        <v/>
+      </c>
+      <c r="J225">
+        <v>1</v>
+      </c>
+      <c r="K225" t="str">
+        <v>2026-07-10T04:31:17.085Z</v>
+      </c>
+      <c r="L225" t="str">
+        <v>Local Dev</v>
+      </c>
+      <c r="M225" t="str">
+        <v>local</v>
+      </c>
+    </row>
+    <row r="226">
+      <c r="A226" t="str">
+        <v>CON-E2E-007</v>
+      </c>
+      <c r="B226" t="str">
+        <v>Click consultant</v>
+      </c>
+      <c r="C226" t="str">
+        <v>Consultant</v>
+      </c>
+      <c r="D226" t="str">
+        <v>Consultant Queue</v>
+      </c>
+      <c r="E226" t="str">
+        <v>DOCTOR</v>
+      </c>
+      <c r="F226" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="G226" t="str">
+        <v>User journey completed successfully</v>
+      </c>
+      <c r="H226" t="str">
+        <v/>
+      </c>
+      <c r="I226" t="str">
+        <v/>
+      </c>
+      <c r="J226">
+        <v>1</v>
+      </c>
+      <c r="K226" t="str">
+        <v>2026-07-10T04:31:17.085Z</v>
+      </c>
+      <c r="L226" t="str">
+        <v>Local Dev</v>
+      </c>
+      <c r="M226" t="str">
+        <v>local</v>
+      </c>
+    </row>
+    <row r="227">
+      <c r="A227" t="str">
+        <v>CON-E2E-008</v>
+      </c>
+      <c r="B227" t="str">
+        <v>Click completed</v>
+      </c>
+      <c r="C227" t="str">
+        <v>Consultant</v>
+      </c>
+      <c r="D227" t="str">
+        <v>Consultant Queue</v>
+      </c>
+      <c r="E227" t="str">
+        <v>DOCTOR</v>
+      </c>
+      <c r="F227" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="G227" t="str">
+        <v>User journey completed successfully</v>
+      </c>
+      <c r="H227" t="str">
+        <v/>
+      </c>
+      <c r="I227" t="str">
+        <v/>
+      </c>
+      <c r="J227">
+        <v>1</v>
+      </c>
+      <c r="K227" t="str">
+        <v>2026-07-10T04:31:17.085Z</v>
+      </c>
+      <c r="L227" t="str">
+        <v>Local Dev</v>
+      </c>
+      <c r="M227" t="str">
+        <v>local</v>
+      </c>
+    </row>
+    <row r="228">
+      <c r="A228" t="str">
+        <v>CON-E2E-009</v>
+      </c>
+      <c r="B228" t="str">
+        <v>Click followup</v>
+      </c>
+      <c r="C228" t="str">
+        <v>Consultant</v>
+      </c>
+      <c r="D228" t="str">
+        <v>Consultant Queue</v>
+      </c>
+      <c r="E228" t="str">
+        <v>DOCTOR</v>
+      </c>
+      <c r="F228" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="G228" t="str">
+        <v>User journey completed successfully</v>
+      </c>
+      <c r="H228" t="str">
+        <v/>
+      </c>
+      <c r="I228" t="str">
+        <v/>
+      </c>
+      <c r="J228">
+        <v>1</v>
+      </c>
+      <c r="K228" t="str">
+        <v>2026-07-10T04:31:17.085Z</v>
+      </c>
+      <c r="L228" t="str">
+        <v>Local Dev</v>
+      </c>
+      <c r="M228" t="str">
+        <v>local</v>
+      </c>
+    </row>
+    <row r="229">
+      <c r="A229" t="str">
+        <v>CON-E2E-010</v>
+      </c>
+      <c r="B229" t="str">
+        <v>Create a Consultant room</v>
+      </c>
+      <c r="C229" t="str">
+        <v>Consultant</v>
+      </c>
+      <c r="D229" t="str">
+        <v>Consultant Queue</v>
+      </c>
+      <c r="E229" t="str">
+        <v>DOCTOR</v>
+      </c>
+      <c r="F229" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="G229" t="str">
+        <v>User journey completed successfully</v>
+      </c>
+      <c r="H229" t="str">
+        <v/>
+      </c>
+      <c r="I229" t="str">
+        <v/>
+      </c>
+      <c r="J229">
+        <v>2</v>
+      </c>
+      <c r="K229" t="str">
+        <v>2026-07-10T04:31:17.085Z</v>
+      </c>
+      <c r="L229" t="str">
+        <v>Local Dev</v>
+      </c>
+      <c r="M229" t="str">
+        <v>local</v>
+      </c>
+    </row>
+    <row r="230">
+      <c r="A230" t="str">
+        <v>BIL-E2E-010</v>
+      </c>
+      <c r="B230" t="str">
+        <v>Search bills</v>
+      </c>
+      <c r="C230" t="str">
+        <v>Billing</v>
+      </c>
+      <c r="D230" t="str">
+        <v>Dashboard</v>
+      </c>
+      <c r="E230" t="str">
+        <v>ACCOUNTANT</v>
+      </c>
+      <c r="F230" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="G230" t="str">
+        <v>User journey completed successfully</v>
+      </c>
+      <c r="H230" t="str">
+        <v/>
+      </c>
+      <c r="I230" t="str">
+        <v/>
+      </c>
+      <c r="J230">
+        <v>1</v>
+      </c>
+      <c r="K230" t="str">
+        <v>2026-07-10T04:31:17.085Z</v>
+      </c>
+      <c r="L230" t="str">
+        <v>Local Dev</v>
+      </c>
+      <c r="M230" t="str">
+        <v>local</v>
+      </c>
+    </row>
+    <row r="231">
+      <c r="A231" t="str">
+        <v>BIL-E2E-011</v>
+      </c>
+      <c r="B231" t="str">
+        <v>Quick bill</v>
+      </c>
+      <c r="C231" t="str">
+        <v>Billing</v>
+      </c>
+      <c r="D231" t="str">
+        <v>Dashboard</v>
+      </c>
+      <c r="E231" t="str">
+        <v>ACCOUNTANT</v>
+      </c>
+      <c r="F231" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="G231" t="str">
+        <v>User journey completed successfully</v>
+      </c>
+      <c r="H231" t="str">
+        <v/>
+      </c>
+      <c r="I231" t="str">
+        <v/>
+      </c>
+      <c r="J231">
+        <v>1</v>
+      </c>
+      <c r="K231" t="str">
+        <v>2026-07-10T04:31:17.085Z</v>
+      </c>
+      <c r="L231" t="str">
+        <v>Local Dev</v>
+      </c>
+      <c r="M231" t="str">
+        <v>local</v>
+      </c>
+    </row>
+    <row r="232">
+      <c r="A232" t="str">
+        <v>BIL-E2E-012</v>
+      </c>
+      <c r="B232" t="str">
+        <v>Add payment methods</v>
+      </c>
+      <c r="C232" t="str">
+        <v>Billing</v>
+      </c>
+      <c r="D232" t="str">
+        <v>Dashboard</v>
+      </c>
+      <c r="E232" t="str">
+        <v>ACCOUNTANT</v>
+      </c>
+      <c r="F232" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="G232" t="str">
+        <v>User journey completed successfully</v>
+      </c>
+      <c r="H232" t="str">
+        <v/>
+      </c>
+      <c r="I232" t="str">
+        <v/>
+      </c>
+      <c r="J232">
+        <v>2</v>
+      </c>
+      <c r="K232" t="str">
+        <v>2026-07-10T04:31:17.085Z</v>
+      </c>
+      <c r="L232" t="str">
+        <v>Local Dev</v>
+      </c>
+      <c r="M232" t="str">
+        <v>local</v>
+      </c>
+    </row>
+    <row r="233">
+      <c r="A233" t="str">
+        <v>BIL-E2E-013</v>
+      </c>
+      <c r="B233" t="str">
+        <v>Add discount</v>
+      </c>
+      <c r="C233" t="str">
+        <v>Billing</v>
+      </c>
+      <c r="D233" t="str">
+        <v>Dashboard</v>
+      </c>
+      <c r="E233" t="str">
+        <v>ACCOUNTANT</v>
+      </c>
+      <c r="F233" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="G233" t="str">
+        <v>User journey completed successfully</v>
+      </c>
+      <c r="H233" t="str">
+        <v/>
+      </c>
+      <c r="I233" t="str">
+        <v/>
+      </c>
+      <c r="J233">
+        <v>2</v>
+      </c>
+      <c r="K233" t="str">
+        <v>2026-07-10T04:31:17.085Z</v>
+      </c>
+      <c r="L233" t="str">
+        <v>Local Dev</v>
+      </c>
+      <c r="M233" t="str">
+        <v>local</v>
+      </c>
+    </row>
+    <row r="234">
+      <c r="A234" t="str">
+        <v>BIL-E2E-014</v>
+      </c>
+      <c r="B234" t="str">
+        <v>Cancel Transaction</v>
+      </c>
+      <c r="C234" t="str">
+        <v>Billing</v>
+      </c>
+      <c r="D234" t="str">
+        <v>Dashboard</v>
+      </c>
+      <c r="E234" t="str">
+        <v>ACCOUNTANT</v>
+      </c>
+      <c r="F234" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="G234" t="str">
+        <v>User journey completed successfully</v>
+      </c>
+      <c r="H234" t="str">
+        <v/>
+      </c>
+      <c r="I234" t="str">
+        <v/>
+      </c>
+      <c r="J234">
+        <v>2</v>
+      </c>
+      <c r="K234" t="str">
+        <v>2026-07-10T04:31:17.085Z</v>
+      </c>
+      <c r="L234" t="str">
+        <v>Local Dev</v>
+      </c>
+      <c r="M234" t="str">
+        <v>local</v>
+      </c>
+    </row>
+    <row r="235">
+      <c r="A235" t="str">
+        <v>BIL-E2E-015</v>
+      </c>
+      <c r="B235" t="str">
+        <v>Pay bill</v>
+      </c>
+      <c r="C235" t="str">
+        <v>Billing</v>
+      </c>
+      <c r="D235" t="str">
+        <v>Dashboard</v>
+      </c>
+      <c r="E235" t="str">
+        <v>ACCOUNTANT</v>
+      </c>
+      <c r="F235" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="G235" t="str">
+        <v>User journey completed successfully</v>
+      </c>
+      <c r="H235" t="str">
+        <v/>
+      </c>
+      <c r="I235" t="str">
+        <v/>
+      </c>
+      <c r="J235">
+        <v>1</v>
+      </c>
+      <c r="K235" t="str">
+        <v>2026-07-10T04:31:17.085Z</v>
+      </c>
+      <c r="L235" t="str">
+        <v>Local Dev</v>
+      </c>
+      <c r="M235" t="str">
+        <v>local</v>
+      </c>
+    </row>
+    <row r="236">
+      <c r="A236" t="str">
+        <v>BIL-E2E-016</v>
+      </c>
+      <c r="B236" t="str">
+        <v>manage  bill</v>
+      </c>
+      <c r="C236" t="str">
+        <v>Billing</v>
+      </c>
+      <c r="D236" t="str">
+        <v>Dashboard</v>
+      </c>
+      <c r="E236" t="str">
+        <v>ACCOUNTANT</v>
+      </c>
+      <c r="F236" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="G236" t="str">
+        <v>User journey completed successfully</v>
+      </c>
+      <c r="H236" t="str">
+        <v/>
+      </c>
+      <c r="I236" t="str">
+        <v/>
+      </c>
+      <c r="J236">
+        <v>1</v>
+      </c>
+      <c r="K236" t="str">
+        <v>2026-07-10T04:31:17.085Z</v>
+      </c>
+      <c r="L236" t="str">
+        <v>Local Dev</v>
+      </c>
+      <c r="M236" t="str">
+        <v>local</v>
+      </c>
+    </row>
+    <row r="237">
+      <c r="A237" t="str">
+        <v>BIL-E2E-017</v>
+      </c>
+      <c r="B237" t="str">
+        <v>Edit bill</v>
+      </c>
+      <c r="C237" t="str">
+        <v>Billing</v>
+      </c>
+      <c r="D237" t="str">
+        <v>Dashboard</v>
+      </c>
+      <c r="E237" t="str">
+        <v>ACCOUNTANT</v>
+      </c>
+      <c r="F237" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="G237" t="str">
+        <v>User journey completed successfully</v>
+      </c>
+      <c r="H237" t="str">
+        <v/>
+      </c>
+      <c r="I237" t="str">
+        <v/>
+      </c>
+      <c r="J237">
+        <v>2</v>
+      </c>
+      <c r="K237" t="str">
+        <v>2026-07-10T04:31:17.085Z</v>
+      </c>
+      <c r="L237" t="str">
+        <v>Local Dev</v>
+      </c>
+      <c r="M237" t="str">
+        <v>local</v>
+      </c>
+    </row>
+    <row r="238">
+      <c r="A238" t="str">
+        <v>APT-E2E-013</v>
+      </c>
+      <c r="B238" t="str">
+        <v>Display patient  status</v>
+      </c>
+      <c r="C238" t="str">
+        <v>Appointments</v>
+      </c>
+      <c r="D238" t="str">
+        <v>Status Logs</v>
+      </c>
+      <c r="E238" t="str">
+        <v>RECEPTIONIST</v>
+      </c>
+      <c r="F238" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="G238" t="str">
+        <v>User journey completed successfully</v>
+      </c>
+      <c r="H238" t="str">
+        <v/>
+      </c>
+      <c r="I238" t="str">
+        <v/>
+      </c>
+      <c r="J238">
+        <v>1</v>
+      </c>
+      <c r="K238" t="str">
+        <v>2026-07-10T04:31:17.085Z</v>
+      </c>
+      <c r="L238" t="str">
+        <v>Local Dev</v>
+      </c>
+      <c r="M238" t="str">
+        <v>local</v>
+      </c>
+    </row>
+    <row r="239">
+      <c r="A239" t="str">
+        <v>APT-E2E-014</v>
+      </c>
+      <c r="B239" t="str">
+        <v>Search patient details</v>
+      </c>
+      <c r="C239" t="str">
+        <v>Appointments</v>
+      </c>
+      <c r="D239" t="str">
+        <v>Appointment History</v>
+      </c>
+      <c r="E239" t="str">
+        <v>RECEPTIONIST</v>
+      </c>
+      <c r="F239" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="G239" t="str">
+        <v>User journey completed successfully</v>
+      </c>
+      <c r="H239" t="str">
+        <v/>
+      </c>
+      <c r="I239" t="str">
+        <v/>
+      </c>
+      <c r="J239">
+        <v>2</v>
+      </c>
+      <c r="K239" t="str">
+        <v>2026-07-10T04:31:17.085Z</v>
+      </c>
+      <c r="L239" t="str">
+        <v>Local Dev</v>
+      </c>
+      <c r="M239" t="str">
+        <v>local</v>
+      </c>
+    </row>
+    <row r="240">
+      <c r="A240" t="str">
+        <v>APT-E2E-015</v>
+      </c>
+      <c r="B240" t="str">
+        <v>Click Go to Queue</v>
+      </c>
+      <c r="C240" t="str">
+        <v>Appointments</v>
+      </c>
+      <c r="D240" t="str">
+        <v>Appointment History</v>
+      </c>
+      <c r="E240" t="str">
+        <v>RECEPTIONIST</v>
+      </c>
+      <c r="F240" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="G240" t="str">
+        <v>User journey completed successfully</v>
+      </c>
+      <c r="H240" t="str">
+        <v/>
+      </c>
+      <c r="I240" t="str">
+        <v/>
+      </c>
+      <c r="J240">
+        <v>1</v>
+      </c>
+      <c r="K240" t="str">
+        <v>2026-07-10T04:31:17.085Z</v>
+      </c>
+      <c r="L240" t="str">
+        <v>Local Dev</v>
+      </c>
+      <c r="M240" t="str">
+        <v>local</v>
+      </c>
+    </row>
+    <row r="241">
+      <c r="A241" t="str">
+        <v>SET-E2E-007</v>
+      </c>
+      <c r="B241" t="str">
+        <v>Add status</v>
+      </c>
+      <c r="C241" t="str">
+        <v>Settings</v>
+      </c>
+      <c r="D241" t="str">
+        <v>Status Config</v>
+      </c>
+      <c r="E241" t="str">
+        <v>ADMIN</v>
+      </c>
+      <c r="F241" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="G241" t="str">
+        <v>User journey completed successfully</v>
+      </c>
+      <c r="H241" t="str">
+        <v/>
+      </c>
+      <c r="I241" t="str">
+        <v/>
+      </c>
+      <c r="J241">
+        <v>2</v>
+      </c>
+      <c r="K241" t="str">
+        <v>2026-07-10T04:31:17.085Z</v>
+      </c>
+      <c r="L241" t="str">
+        <v>Local Dev</v>
+      </c>
+      <c r="M241" t="str">
+        <v>local</v>
+      </c>
+    </row>
+    <row r="242">
+      <c r="A242" t="str">
+        <v>SET-E2E-008</v>
+      </c>
+      <c r="B242" t="str">
+        <v>Create a Organization</v>
+      </c>
+      <c r="C242" t="str">
+        <v>Settings</v>
+      </c>
+      <c r="D242" t="str">
+        <v>Organization</v>
+      </c>
+      <c r="E242" t="str">
+        <v>ADMIN</v>
+      </c>
+      <c r="F242" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="G242" t="str">
+        <v>User journey completed successfully</v>
+      </c>
+      <c r="H242" t="str">
+        <v/>
+      </c>
+      <c r="I242" t="str">
+        <v/>
+      </c>
+      <c r="J242">
+        <v>1</v>
+      </c>
+      <c r="K242" t="str">
+        <v>2026-07-10T04:31:17.085Z</v>
+      </c>
+      <c r="L242" t="str">
+        <v>Local Dev</v>
+      </c>
+      <c r="M242" t="str">
+        <v>local</v>
+      </c>
+    </row>
+    <row r="243">
+      <c r="A243" t="str">
+        <v>SET-E2E-009</v>
+      </c>
+      <c r="B243" t="str">
+        <v>Create a location</v>
+      </c>
+      <c r="C243" t="str">
+        <v>Settings</v>
+      </c>
+      <c r="D243" t="str">
+        <v>Locations</v>
+      </c>
+      <c r="E243" t="str">
+        <v>ADMIN</v>
+      </c>
+      <c r="F243" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="G243" t="str">
+        <v>User journey completed successfully</v>
+      </c>
+      <c r="H243" t="str">
+        <v/>
+      </c>
+      <c r="I243" t="str">
+        <v/>
+      </c>
+      <c r="J243">
+        <v>1</v>
+      </c>
+      <c r="K243" t="str">
+        <v>2026-07-10T04:31:17.085Z</v>
+      </c>
+      <c r="L243" t="str">
+        <v>Local Dev</v>
+      </c>
+      <c r="M243" t="str">
+        <v>local</v>
+      </c>
+    </row>
+    <row r="244">
+      <c r="A244" t="str">
+        <v>SET-E2E-010</v>
+      </c>
+      <c r="B244" t="str">
+        <v>Edit Location</v>
+      </c>
+      <c r="C244" t="str">
+        <v>Settings</v>
+      </c>
+      <c r="D244" t="str">
+        <v>Locations</v>
+      </c>
+      <c r="E244" t="str">
+        <v>ADMIN</v>
+      </c>
+      <c r="F244" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="G244" t="str">
+        <v>User journey completed successfully</v>
+      </c>
+      <c r="H244" t="str">
+        <v/>
+      </c>
+      <c r="I244" t="str">
+        <v/>
+      </c>
+      <c r="J244">
+        <v>1</v>
+      </c>
+      <c r="K244" t="str">
+        <v>2026-07-10T04:31:17.085Z</v>
+      </c>
+      <c r="L244" t="str">
+        <v>Local Dev</v>
+      </c>
+      <c r="M244" t="str">
+        <v>local</v>
+      </c>
+    </row>
+    <row r="245">
+      <c r="A245" t="str">
+        <v>SET-E2E-011</v>
+      </c>
+      <c r="B245" t="str">
+        <v>Display Staff list</v>
+      </c>
+      <c r="C245" t="str">
+        <v>Settings</v>
+      </c>
+      <c r="D245" t="str">
+        <v>Users</v>
+      </c>
+      <c r="E245" t="str">
+        <v>ADMIN</v>
+      </c>
+      <c r="F245" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="G245" t="str">
+        <v>User journey completed successfully</v>
+      </c>
+      <c r="H245" t="str">
+        <v/>
+      </c>
+      <c r="I245" t="str">
+        <v/>
+      </c>
+      <c r="J245">
+        <v>2</v>
+      </c>
+      <c r="K245" t="str">
+        <v>2026-07-10T04:31:17.085Z</v>
+      </c>
+      <c r="L245" t="str">
+        <v>Local Dev</v>
+      </c>
+      <c r="M245" t="str">
+        <v>local</v>
+      </c>
+    </row>
+    <row r="246">
+      <c r="A246" t="str">
+        <v>SET-E2E-012</v>
+      </c>
+      <c r="B246" t="str">
+        <v>Invite by Email</v>
+      </c>
+      <c r="C246" t="str">
+        <v>Settings</v>
+      </c>
+      <c r="D246" t="str">
+        <v>Users</v>
+      </c>
+      <c r="E246" t="str">
+        <v>ADMIN</v>
+      </c>
+      <c r="F246" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="G246" t="str">
+        <v>User journey completed successfully</v>
+      </c>
+      <c r="H246" t="str">
+        <v/>
+      </c>
+      <c r="I246" t="str">
+        <v/>
+      </c>
+      <c r="J246">
+        <v>2</v>
+      </c>
+      <c r="K246" t="str">
+        <v>2026-07-10T04:31:17.085Z</v>
+      </c>
+      <c r="L246" t="str">
+        <v>Local Dev</v>
+      </c>
+      <c r="M246" t="str">
+        <v>local</v>
+      </c>
+    </row>
+    <row r="247">
+      <c r="A247" t="str">
+        <v>SET-E2E-013</v>
+      </c>
+      <c r="B247" t="str">
+        <v>Invite by SMS</v>
+      </c>
+      <c r="C247" t="str">
+        <v>Settings</v>
+      </c>
+      <c r="D247" t="str">
+        <v>Users</v>
+      </c>
+      <c r="E247" t="str">
+        <v>ADMIN</v>
+      </c>
+      <c r="F247" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="G247" t="str">
+        <v>User journey completed successfully</v>
+      </c>
+      <c r="H247" t="str">
+        <v/>
+      </c>
+      <c r="I247" t="str">
+        <v/>
+      </c>
+      <c r="J247">
+        <v>4</v>
+      </c>
+      <c r="K247" t="str">
+        <v>2026-07-10T04:31:17.085Z</v>
+      </c>
+      <c r="L247" t="str">
+        <v>Local Dev</v>
+      </c>
+      <c r="M247" t="str">
+        <v>local</v>
+      </c>
+    </row>
+    <row r="248">
+      <c r="A248" t="str">
+        <v>CON-E2E-011</v>
+      </c>
+      <c r="B248" t="str">
+        <v>Add a  column</v>
+      </c>
+      <c r="C248" t="str">
+        <v>Consultant</v>
+      </c>
+      <c r="D248" t="str">
+        <v>Consultant Room</v>
+      </c>
+      <c r="E248" t="str">
+        <v>DOCTOR</v>
+      </c>
+      <c r="F248" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="G248" t="str">
+        <v>User journey completed successfully</v>
+      </c>
+      <c r="H248" t="str">
+        <v/>
+      </c>
+      <c r="I248" t="str">
+        <v/>
+      </c>
+      <c r="J248">
+        <v>2</v>
+      </c>
+      <c r="K248" t="str">
+        <v>2026-07-10T04:31:17.085Z</v>
+      </c>
+      <c r="L248" t="str">
+        <v>Local Dev</v>
+      </c>
+      <c r="M248" t="str">
+        <v>local</v>
+      </c>
+    </row>
+    <row r="249">
+      <c r="A249" t="str">
+        <v>DIS-E2E-005</v>
+      </c>
+      <c r="B249" t="str">
+        <v>Display Patient queue screen preview</v>
+      </c>
+      <c r="C249" t="str">
+        <v>Display</v>
+      </c>
+      <c r="D249" t="str">
+        <v>TV Display</v>
+      </c>
+      <c r="E249" t="str">
+        <v>STANDARD</v>
+      </c>
+      <c r="F249" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="G249" t="str">
+        <v>User journey completed successfully</v>
+      </c>
+      <c r="H249" t="str">
+        <v/>
+      </c>
+      <c r="I249" t="str">
+        <v/>
+      </c>
+      <c r="J249">
+        <v>2</v>
+      </c>
+      <c r="K249" t="str">
+        <v>2026-07-10T04:31:17.085Z</v>
+      </c>
+      <c r="L249" t="str">
+        <v>Local Dev</v>
+      </c>
+      <c r="M249" t="str">
+        <v>local</v>
+      </c>
+    </row>
+    <row r="250">
+      <c r="A250" t="str">
+        <v>SET-E2E-014</v>
+      </c>
+      <c r="B250" t="str">
+        <v>Create  new SMS event</v>
+      </c>
+      <c r="C250" t="str">
+        <v>Settings</v>
+      </c>
+      <c r="D250" t="str">
+        <v>SMS Configuration</v>
+      </c>
+      <c r="E250" t="str">
+        <v>ADMIN</v>
+      </c>
+      <c r="F250" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="G250" t="str">
+        <v>User journey completed successfully</v>
+      </c>
+      <c r="H250" t="str">
+        <v/>
+      </c>
+      <c r="I250" t="str">
+        <v/>
+      </c>
+      <c r="J250">
+        <v>2</v>
+      </c>
+      <c r="K250" t="str">
+        <v>2026-07-10T04:31:17.085Z</v>
+      </c>
+      <c r="L250" t="str">
+        <v>Local Dev</v>
+      </c>
+      <c r="M250" t="str">
+        <v>local</v>
+      </c>
+    </row>
+    <row r="251">
+      <c r="A251" t="str">
+        <v>SET-E2E-015</v>
+      </c>
+      <c r="B251" t="str">
+        <v>Add New Visit Purpose</v>
+      </c>
+      <c r="C251" t="str">
+        <v>Settings</v>
+      </c>
+      <c r="D251" t="str">
+        <v>Visit Purposes</v>
+      </c>
+      <c r="E251" t="str">
+        <v>ADMIN</v>
+      </c>
+      <c r="F251" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="G251" t="str">
+        <v>User journey completed successfully</v>
+      </c>
+      <c r="H251" t="str">
+        <v/>
+      </c>
+      <c r="I251" t="str">
+        <v/>
+      </c>
+      <c r="J251">
+        <v>2</v>
+      </c>
+      <c r="K251" t="str">
+        <v>2026-07-10T04:31:17.085Z</v>
+      </c>
+      <c r="L251" t="str">
+        <v>Local Dev</v>
+      </c>
+      <c r="M251" t="str">
+        <v>local</v>
+      </c>
+    </row>
+    <row r="252">
+      <c r="A252" t="str">
+        <v>SET-E2E-016</v>
+      </c>
+      <c r="B252" t="str">
+        <v>Disable active Purpose</v>
+      </c>
+      <c r="C252" t="str">
+        <v>Settings</v>
+      </c>
+      <c r="D252" t="str">
+        <v>Visit Purposes</v>
+      </c>
+      <c r="E252" t="str">
+        <v>ADMIN</v>
+      </c>
+      <c r="F252" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="G252" t="str">
+        <v>User journey completed successfully</v>
+      </c>
+      <c r="H252" t="str">
+        <v/>
+      </c>
+      <c r="I252" t="str">
+        <v/>
+      </c>
+      <c r="J252">
+        <v>2</v>
+      </c>
+      <c r="K252" t="str">
+        <v>2026-07-10T04:31:17.085Z</v>
+      </c>
+      <c r="L252" t="str">
+        <v>Local Dev</v>
+      </c>
+      <c r="M252" t="str">
+        <v>local</v>
+      </c>
+    </row>
+    <row r="253">
+      <c r="A253" t="str">
+        <v>SET-E2E-017</v>
+      </c>
+      <c r="B253" t="str">
+        <v>Edit Visit Purpose</v>
+      </c>
+      <c r="C253" t="str">
+        <v>Settings</v>
+      </c>
+      <c r="D253" t="str">
+        <v>Visit Purposes</v>
+      </c>
+      <c r="E253" t="str">
+        <v>ADMIN</v>
+      </c>
+      <c r="F253" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="G253" t="str">
+        <v>User journey completed successfully</v>
+      </c>
+      <c r="H253" t="str">
+        <v/>
+      </c>
+      <c r="I253" t="str">
+        <v/>
+      </c>
+      <c r="J253">
+        <v>4</v>
+      </c>
+      <c r="K253" t="str">
+        <v>2026-07-10T04:31:17.085Z</v>
+      </c>
+      <c r="L253" t="str">
+        <v>Local Dev</v>
+      </c>
+      <c r="M253" t="str">
+        <v>local</v>
+      </c>
+    </row>
+    <row r="254">
+      <c r="A254" t="str">
+        <v>SET-E2E-018</v>
+      </c>
+      <c r="B254" t="str">
+        <v>Add Service</v>
+      </c>
+      <c r="C254" t="str">
+        <v>Settings</v>
+      </c>
+      <c r="D254" t="str">
+        <v>Services</v>
+      </c>
+      <c r="E254" t="str">
+        <v>ADMIN</v>
+      </c>
+      <c r="F254" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="G254" t="str">
+        <v>User journey completed successfully</v>
+      </c>
+      <c r="H254" t="str">
+        <v/>
+      </c>
+      <c r="I254" t="str">
+        <v/>
+      </c>
+      <c r="J254">
+        <v>2</v>
+      </c>
+      <c r="K254" t="str">
+        <v>2026-07-10T04:31:17.085Z</v>
+      </c>
+      <c r="L254" t="str">
+        <v>Local Dev</v>
+      </c>
+      <c r="M254" t="str">
+        <v>local</v>
+      </c>
+    </row>
+    <row r="255">
+      <c r="A255" t="str">
+        <v>SET-E2E-019</v>
+      </c>
+      <c r="B255" t="str">
+        <v>Edit Service</v>
+      </c>
+      <c r="C255" t="str">
+        <v>Settings</v>
+      </c>
+      <c r="D255" t="str">
+        <v>Services</v>
+      </c>
+      <c r="E255" t="str">
+        <v>ADMIN</v>
+      </c>
+      <c r="F255" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="G255" t="str">
+        <v>User journey completed successfully</v>
+      </c>
+      <c r="H255" t="str">
+        <v/>
+      </c>
+      <c r="I255" t="str">
+        <v/>
+      </c>
+      <c r="J255">
+        <v>2</v>
+      </c>
+      <c r="K255" t="str">
+        <v>2026-07-10T04:31:17.085Z</v>
+      </c>
+      <c r="L255" t="str">
+        <v>Local Dev</v>
+      </c>
+      <c r="M255" t="str">
+        <v>local</v>
+      </c>
+    </row>
+    <row r="256">
+      <c r="A256" t="str">
+        <v>SET-E2E-020</v>
+      </c>
+      <c r="B256" t="str">
+        <v>Create a new SMS Configuration</v>
+      </c>
+      <c r="C256" t="str">
+        <v>Settings</v>
+      </c>
+      <c r="D256" t="str">
+        <v>SMS Configuration</v>
+      </c>
+      <c r="E256" t="str">
+        <v>ADMIN</v>
+      </c>
+      <c r="F256" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="G256" t="str">
+        <v>User journey completed successfully</v>
+      </c>
+      <c r="H256" t="str">
+        <v/>
+      </c>
+      <c r="I256" t="str">
+        <v/>
+      </c>
+      <c r="J256">
+        <v>1</v>
+      </c>
+      <c r="K256" t="str">
+        <v>2026-07-10T04:31:17.085Z</v>
+      </c>
+      <c r="L256" t="str">
+        <v>Local Dev</v>
+      </c>
+      <c r="M256" t="str">
+        <v>local</v>
+      </c>
+    </row>
+    <row r="257">
+      <c r="A257" t="str">
+        <v>SET-E2E-021</v>
+      </c>
+      <c r="B257" t="str">
+        <v>Create a new template</v>
+      </c>
+      <c r="C257" t="str">
+        <v>Settings</v>
+      </c>
+      <c r="D257" t="str">
+        <v>WhatsApp Configuration</v>
+      </c>
+      <c r="E257" t="str">
+        <v>ADMIN</v>
+      </c>
+      <c r="F257" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="G257" t="str">
+        <v>User journey completed successfully</v>
+      </c>
+      <c r="H257" t="str">
+        <v/>
+      </c>
+      <c r="I257" t="str">
+        <v/>
+      </c>
+      <c r="J257">
+        <v>2</v>
+      </c>
+      <c r="K257" t="str">
+        <v>2026-07-10T04:31:17.085Z</v>
+      </c>
+      <c r="L257" t="str">
+        <v>Local Dev</v>
+      </c>
+      <c r="M257" t="str">
+        <v>local</v>
+      </c>
+    </row>
+    <row r="258">
+      <c r="A258" t="str">
+        <v>SET-E2E-022</v>
+      </c>
+      <c r="B258" t="str">
+        <v>testing whatsapp message</v>
+      </c>
+      <c r="C258" t="str">
+        <v>Settings</v>
+      </c>
+      <c r="D258" t="str">
+        <v>WhatsApp Configuration</v>
+      </c>
+      <c r="E258" t="str">
+        <v>ADMIN</v>
+      </c>
+      <c r="F258" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="G258" t="str">
+        <v>User journey completed successfully</v>
+      </c>
+      <c r="H258" t="str">
+        <v/>
+      </c>
+      <c r="I258" t="str">
+        <v/>
+      </c>
+      <c r="J258">
+        <v>2</v>
+      </c>
+      <c r="K258" t="str">
+        <v>2026-07-10T04:31:17.085Z</v>
+      </c>
+      <c r="L258" t="str">
+        <v>Local Dev</v>
+      </c>
+      <c r="M258" t="str">
+        <v>local</v>
+      </c>
+    </row>
+    <row r="259">
+      <c r="A259" t="str">
+        <v>SET-E2E-023</v>
+      </c>
+      <c r="B259" t="str">
+        <v>TESTING</v>
+      </c>
+      <c r="C259" t="str">
+        <v>Settings</v>
+      </c>
+      <c r="D259" t="str">
+        <v>WhatsApp Configuration</v>
+      </c>
+      <c r="E259" t="str">
+        <v>ADMIN</v>
+      </c>
+      <c r="F259" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="G259" t="str">
+        <v>User journey completed successfully</v>
+      </c>
+      <c r="H259" t="str">
+        <v/>
+      </c>
+      <c r="I259" t="str">
+        <v/>
+      </c>
+      <c r="J259">
+        <v>2</v>
+      </c>
+      <c r="K259" t="str">
+        <v>2026-07-10T04:31:17.085Z</v>
+      </c>
+      <c r="L259" t="str">
+        <v>Local Dev</v>
+      </c>
+      <c r="M259" t="str">
+        <v>local</v>
+      </c>
+    </row>
+    <row r="260">
+      <c r="A260" t="str">
+        <v>LOG-E2E-001</v>
+      </c>
+      <c r="B260" t="str">
+        <v>Display monitoring and reviews</v>
+      </c>
+      <c r="C260" t="str">
+        <v>Applogs</v>
+      </c>
+      <c r="D260" t="str">
+        <v>App Logs</v>
+      </c>
+      <c r="E260" t="str">
+        <v>ADMIN</v>
+      </c>
+      <c r="F260" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="G260" t="str">
+        <v>User journey completed successfully</v>
+      </c>
+      <c r="H260" t="str">
+        <v/>
+      </c>
+      <c r="I260" t="str">
+        <v/>
+      </c>
+      <c r="J260">
+        <v>2</v>
+      </c>
+      <c r="K260" t="str">
+        <v>2026-07-10T04:31:17.085Z</v>
+      </c>
+      <c r="L260" t="str">
+        <v>Local Dev</v>
+      </c>
+      <c r="M260" t="str">
+        <v>local</v>
+      </c>
+    </row>
+    <row r="261">
+      <c r="A261" t="str">
+        <v>SET-E2E-024</v>
+      </c>
+      <c r="B261" t="str">
+        <v>Configure and manage your booking config</v>
+      </c>
+      <c r="C261" t="str">
+        <v>Settings</v>
+      </c>
+      <c r="D261" t="str">
+        <v>Booking Configuration</v>
+      </c>
+      <c r="E261" t="str">
+        <v>ADMIN</v>
+      </c>
+      <c r="F261" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="G261" t="str">
+        <v>User journey completed successfully</v>
+      </c>
+      <c r="H261" t="str">
+        <v/>
+      </c>
+      <c r="I261" t="str">
+        <v/>
+      </c>
+      <c r="J261">
+        <v>2</v>
+      </c>
+      <c r="K261" t="str">
+        <v>2026-07-10T04:31:17.085Z</v>
+      </c>
+      <c r="L261" t="str">
+        <v>Local Dev</v>
+      </c>
+      <c r="M261" t="str">
+        <v>local</v>
+      </c>
+    </row>
+    <row r="262">
+      <c r="A262" t="str">
+        <v>BIL-E2E-018</v>
+      </c>
+      <c r="B262" t="str">
+        <v>Show invoice report</v>
+      </c>
+      <c r="C262" t="str">
+        <v>Billing</v>
+      </c>
+      <c r="D262" t="str">
+        <v>Invoice Reports</v>
+      </c>
+      <c r="E262" t="str">
+        <v>ACCOUNTANT</v>
+      </c>
+      <c r="F262" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="G262" t="str">
+        <v>User journey completed successfully</v>
+      </c>
+      <c r="H262" t="str">
+        <v/>
+      </c>
+      <c r="I262" t="str">
+        <v/>
+      </c>
+      <c r="J262">
+        <v>2</v>
+      </c>
+      <c r="K262" t="str">
+        <v>2026-07-10T04:31:17.085Z</v>
+      </c>
+      <c r="L262" t="str">
+        <v>Local Dev</v>
+      </c>
+      <c r="M262" t="str">
+        <v>local</v>
+      </c>
+    </row>
+    <row r="263">
+      <c r="A263" t="str">
+        <v>BIL-E2E-019</v>
+      </c>
+      <c r="B263" t="str">
+        <v>Check invoice report of patient</v>
+      </c>
+      <c r="C263" t="str">
+        <v>Billing</v>
+      </c>
+      <c r="D263" t="str">
+        <v>Invoice Reports</v>
+      </c>
+      <c r="E263" t="str">
+        <v>ACCOUNTANT</v>
+      </c>
+      <c r="F263" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="G263" t="str">
+        <v>User journey completed successfully</v>
+      </c>
+      <c r="H263" t="str">
+        <v/>
+      </c>
+      <c r="I263" t="str">
+        <v/>
+      </c>
+      <c r="J263">
+        <v>1</v>
+      </c>
+      <c r="K263" t="str">
+        <v>2026-07-10T04:31:17.085Z</v>
+      </c>
+      <c r="L263" t="str">
+        <v>Local Dev</v>
+      </c>
+      <c r="M263" t="str">
+        <v>local</v>
+      </c>
+    </row>
+    <row r="264">
+      <c r="A264" t="str">
+        <v>BIL-E2E-020</v>
+      </c>
+      <c r="B264" t="str">
+        <v>show updated details of patients</v>
+      </c>
+      <c r="C264" t="str">
+        <v>Billing</v>
+      </c>
+      <c r="D264" t="str">
+        <v>Invoice Reports</v>
+      </c>
+      <c r="E264" t="str">
+        <v>ACCOUNTANT</v>
+      </c>
+      <c r="F264" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="G264" t="str">
+        <v>User journey completed successfully</v>
+      </c>
+      <c r="H264" t="str">
+        <v/>
+      </c>
+      <c r="I264" t="str">
+        <v/>
+      </c>
+      <c r="J264">
+        <v>2</v>
+      </c>
+      <c r="K264" t="str">
+        <v>2026-07-10T04:31:17.085Z</v>
+      </c>
+      <c r="L264" t="str">
+        <v>Local Dev</v>
+      </c>
+      <c r="M264" t="str">
+        <v>local</v>
+      </c>
+    </row>
+    <row r="265">
+      <c r="A265" t="str">
+        <v>BIL-E2E-021</v>
+      </c>
+      <c r="B265" t="str">
+        <v>Search patient reports</v>
+      </c>
+      <c r="C265" t="str">
+        <v>Billing</v>
+      </c>
+      <c r="D265" t="str">
+        <v>Invoice Reports</v>
+      </c>
+      <c r="E265" t="str">
+        <v>ACCOUNTANT</v>
+      </c>
+      <c r="F265" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="G265" t="str">
+        <v>User journey completed successfully</v>
+      </c>
+      <c r="H265" t="str">
+        <v/>
+      </c>
+      <c r="I265" t="str">
+        <v/>
+      </c>
+      <c r="J265">
+        <v>2</v>
+      </c>
+      <c r="K265" t="str">
+        <v>2026-07-10T04:31:17.085Z</v>
+      </c>
+      <c r="L265" t="str">
+        <v>Local Dev</v>
+      </c>
+      <c r="M265" t="str">
+        <v>local</v>
+      </c>
+    </row>
+    <row r="266">
+      <c r="A266" t="str">
+        <v>BIL-E2E-022</v>
+      </c>
+      <c r="B266" t="str">
+        <v>Day invoices</v>
+      </c>
+      <c r="C266" t="str">
+        <v>Billing</v>
+      </c>
+      <c r="D266" t="str">
+        <v>Invoice Reports</v>
+      </c>
+      <c r="E266" t="str">
+        <v>ACCOUNTANT</v>
+      </c>
+      <c r="F266" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="G266" t="str">
+        <v>User journey completed successfully</v>
+      </c>
+      <c r="H266" t="str">
+        <v/>
+      </c>
+      <c r="I266" t="str">
+        <v/>
+      </c>
+      <c r="J266">
+        <v>2</v>
+      </c>
+      <c r="K266" t="str">
+        <v>2026-07-10T04:31:17.085Z</v>
+      </c>
+      <c r="L266" t="str">
+        <v>Local Dev</v>
+      </c>
+      <c r="M266" t="str">
+        <v>local</v>
+      </c>
+    </row>
+    <row r="267">
+      <c r="A267" t="str">
+        <v>BIL-E2E-023</v>
+      </c>
+      <c r="B267" t="str">
+        <v>Day summary</v>
+      </c>
+      <c r="C267" t="str">
+        <v>Billing</v>
+      </c>
+      <c r="D267" t="str">
+        <v>Invoice Reports</v>
+      </c>
+      <c r="E267" t="str">
+        <v>ACCOUNTANT</v>
+      </c>
+      <c r="F267" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="G267" t="str">
+        <v>User journey completed successfully</v>
+      </c>
+      <c r="H267" t="str">
+        <v/>
+      </c>
+      <c r="I267" t="str">
+        <v/>
+      </c>
+      <c r="J267">
+        <v>1</v>
+      </c>
+      <c r="K267" t="str">
+        <v>2026-07-10T04:31:17.085Z</v>
+      </c>
+      <c r="L267" t="str">
+        <v>Local Dev</v>
+      </c>
+      <c r="M267" t="str">
+        <v>local</v>
+      </c>
+    </row>
+    <row r="268">
+      <c r="A268" t="str">
+        <v>BIL-E2E-024</v>
+      </c>
+      <c r="B268" t="str">
+        <v>SETTIEMENT REPORT</v>
+      </c>
+      <c r="C268" t="str">
+        <v>Billing</v>
+      </c>
+      <c r="D268" t="str">
+        <v>Invoice Reports</v>
+      </c>
+      <c r="E268" t="str">
+        <v>ACCOUNTANT</v>
+      </c>
+      <c r="F268" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="G268" t="str">
+        <v>User journey completed successfully</v>
+      </c>
+      <c r="H268" t="str">
+        <v/>
+      </c>
+      <c r="I268" t="str">
+        <v/>
+      </c>
+      <c r="J268">
+        <v>2</v>
+      </c>
+      <c r="K268" t="str">
+        <v>2026-07-10T04:31:17.085Z</v>
+      </c>
+      <c r="L268" t="str">
+        <v>Local Dev</v>
+      </c>
+      <c r="M268" t="str">
+        <v>local</v>
+      </c>
+    </row>
+    <row r="269">
+      <c r="A269" t="str">
+        <v>BIL-E2E-025</v>
+      </c>
+      <c r="B269" t="str">
+        <v>DISCOUNTS</v>
+      </c>
+      <c r="C269" t="str">
+        <v>Billing</v>
+      </c>
+      <c r="D269" t="str">
+        <v>Invoice Reports</v>
+      </c>
+      <c r="E269" t="str">
+        <v>ACCOUNTANT</v>
+      </c>
+      <c r="F269" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="G269" t="str">
+        <v>User journey completed successfully</v>
+      </c>
+      <c r="H269" t="str">
+        <v/>
+      </c>
+      <c r="I269" t="str">
+        <v/>
+      </c>
+      <c r="J269">
+        <v>2</v>
+      </c>
+      <c r="K269" t="str">
+        <v>2026-07-10T04:31:17.085Z</v>
+      </c>
+      <c r="L269" t="str">
+        <v>Local Dev</v>
+      </c>
+      <c r="M269" t="str">
+        <v>local</v>
+      </c>
+    </row>
+    <row r="270">
+      <c r="A270" t="str">
+        <v>BIL-E2E-026</v>
+      </c>
+      <c r="B270" t="str">
+        <v>DUES PAID</v>
+      </c>
+      <c r="C270" t="str">
+        <v>Billing</v>
+      </c>
+      <c r="D270" t="str">
+        <v>Invoice Reports</v>
+      </c>
+      <c r="E270" t="str">
+        <v>ACCOUNTANT</v>
+      </c>
+      <c r="F270" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="G270" t="str">
+        <v>User journey completed successfully</v>
+      </c>
+      <c r="H270" t="str">
+        <v/>
+      </c>
+      <c r="I270" t="str">
+        <v/>
+      </c>
+      <c r="J270">
+        <v>1</v>
+      </c>
+      <c r="K270" t="str">
+        <v>2026-07-10T04:31:17.085Z</v>
+      </c>
+      <c r="L270" t="str">
+        <v>Local Dev</v>
+      </c>
+      <c r="M270" t="str">
+        <v>local</v>
+      </c>
+    </row>
+    <row r="271">
+      <c r="A271" t="str">
+        <v>BIL-E2E-027</v>
+      </c>
+      <c r="B271" t="str">
+        <v>Physical cash settlement</v>
+      </c>
+      <c r="C271" t="str">
+        <v>Billing</v>
+      </c>
+      <c r="D271" t="str">
+        <v>Daily Cash</v>
+      </c>
+      <c r="E271" t="str">
+        <v>ACCOUNTANT</v>
+      </c>
+      <c r="F271" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="G271" t="str">
+        <v>User journey completed successfully</v>
+      </c>
+      <c r="H271" t="str">
+        <v/>
+      </c>
+      <c r="I271" t="str">
+        <v/>
+      </c>
+      <c r="J271">
+        <v>1</v>
+      </c>
+      <c r="K271" t="str">
+        <v>2026-07-10T04:31:17.085Z</v>
+      </c>
+      <c r="L271" t="str">
+        <v>Local Dev</v>
+      </c>
+      <c r="M271" t="str">
+        <v>local</v>
+      </c>
+    </row>
+    <row r="272">
+      <c r="A272" t="str">
+        <v>BIL-E2E-028</v>
+      </c>
+      <c r="B272" t="str">
+        <v>Payment log</v>
+      </c>
+      <c r="C272" t="str">
+        <v>Billing</v>
+      </c>
+      <c r="D272" t="str">
+        <v>Daily Cash</v>
+      </c>
+      <c r="E272" t="str">
+        <v>ACCOUNTANT</v>
+      </c>
+      <c r="F272" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="G272" t="str">
+        <v>User journey completed successfully</v>
+      </c>
+      <c r="H272" t="str">
+        <v/>
+      </c>
+      <c r="I272" t="str">
+        <v/>
+      </c>
+      <c r="J272">
+        <v>2</v>
+      </c>
+      <c r="K272" t="str">
+        <v>2026-07-10T04:31:17.085Z</v>
+      </c>
+      <c r="L272" t="str">
+        <v>Local Dev</v>
+      </c>
+      <c r="M272" t="str">
+        <v>local</v>
+      </c>
+    </row>
+    <row r="273">
+      <c r="A273" t="str">
+        <v>FOL-E2E-005</v>
+      </c>
+      <c r="B273" t="str">
+        <v>Track And Manage Patient Follow-Ups</v>
+      </c>
+      <c r="C273" t="str">
+        <v>Follow-Ups</v>
+      </c>
+      <c r="D273" t="str">
+        <v>Dashboard</v>
+      </c>
+      <c r="E273" t="str">
+        <v>STANDARD</v>
+      </c>
+      <c r="F273" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="G273" t="str">
+        <v>User journey completed successfully</v>
+      </c>
+      <c r="H273" t="str">
+        <v/>
+      </c>
+      <c r="I273" t="str">
+        <v/>
+      </c>
+      <c r="J273">
+        <v>1</v>
+      </c>
+      <c r="K273" t="str">
+        <v>2026-07-10T04:31:17.085Z</v>
+      </c>
+      <c r="L273" t="str">
+        <v>Local Dev</v>
+      </c>
+      <c r="M273" t="str">
+        <v>local</v>
+      </c>
+    </row>
+    <row r="274">
+      <c r="A274" t="str">
+        <v>TSK-E2E-002</v>
+      </c>
+      <c r="B274" t="str">
+        <v>Track, schedule, and complete daily clinic operations</v>
+      </c>
+      <c r="C274" t="str">
+        <v>Tasks</v>
+      </c>
+      <c r="D274" t="str">
+        <v>Dashboard</v>
+      </c>
+      <c r="E274" t="str">
+        <v>STANDARD</v>
+      </c>
+      <c r="F274" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="G274" t="str">
+        <v>User journey completed successfully</v>
+      </c>
+      <c r="H274" t="str">
+        <v/>
+      </c>
+      <c r="I274" t="str">
+        <v/>
+      </c>
+      <c r="J274">
+        <v>3</v>
+      </c>
+      <c r="K274" t="str">
+        <v>2026-07-10T04:31:17.085Z</v>
+      </c>
+      <c r="L274" t="str">
+        <v>Local Dev</v>
+      </c>
+      <c r="M274" t="str">
+        <v>local</v>
+      </c>
+    </row>
+    <row r="275">
+      <c r="A275" t="str">
+        <v>TSK-E2E-003</v>
+      </c>
+      <c r="B275" t="str">
+        <v>Add task</v>
+      </c>
+      <c r="C275" t="str">
+        <v>Tasks</v>
+      </c>
+      <c r="D275" t="str">
+        <v>Dashboard</v>
+      </c>
+      <c r="E275" t="str">
+        <v>STANDARD</v>
+      </c>
+      <c r="F275" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="G275" t="str">
+        <v>User journey completed successfully</v>
+      </c>
+      <c r="H275" t="str">
+        <v/>
+      </c>
+      <c r="I275" t="str">
+        <v/>
+      </c>
+      <c r="J275">
+        <v>2</v>
+      </c>
+      <c r="K275" t="str">
+        <v>2026-07-10T04:31:17.085Z</v>
+      </c>
+      <c r="L275" t="str">
+        <v>Local Dev</v>
+      </c>
+      <c r="M275" t="str">
+        <v>local</v>
+      </c>
+    </row>
+    <row r="276">
+      <c r="A276" t="str">
+        <v>TSK-E2E-004</v>
+      </c>
+      <c r="B276" t="str">
+        <v>view the calender</v>
+      </c>
+      <c r="C276" t="str">
+        <v>Tasks</v>
+      </c>
+      <c r="D276" t="str">
+        <v>Dashboard</v>
+      </c>
+      <c r="E276" t="str">
+        <v>STANDARD</v>
+      </c>
+      <c r="F276" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="G276" t="str">
+        <v>User journey completed successfully</v>
+      </c>
+      <c r="H276" t="str">
+        <v/>
+      </c>
+      <c r="I276" t="str">
+        <v/>
+      </c>
+      <c r="J276">
+        <v>1</v>
+      </c>
+      <c r="K276" t="str">
+        <v>2026-07-10T04:31:17.085Z</v>
+      </c>
+      <c r="L276" t="str">
+        <v>Local Dev</v>
+      </c>
+      <c r="M276" t="str">
+        <v>local</v>
+      </c>
+    </row>
+    <row r="277">
+      <c r="A277" t="str">
+        <v>TSK-E2E-005</v>
+      </c>
+      <c r="B277" t="str">
+        <v>View the categories</v>
+      </c>
+      <c r="C277" t="str">
+        <v>Tasks</v>
+      </c>
+      <c r="D277" t="str">
+        <v>Dashboard</v>
+      </c>
+      <c r="E277" t="str">
+        <v>STANDARD</v>
+      </c>
+      <c r="F277" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="G277" t="str">
+        <v>User journey completed successfully</v>
+      </c>
+      <c r="H277" t="str">
+        <v/>
+      </c>
+      <c r="I277" t="str">
+        <v/>
+      </c>
+      <c r="J277">
+        <v>2</v>
+      </c>
+      <c r="K277" t="str">
+        <v>2026-07-10T04:31:17.085Z</v>
+      </c>
+      <c r="L277" t="str">
+        <v>Local Dev</v>
+      </c>
+      <c r="M277" t="str">
+        <v>local</v>
+      </c>
+    </row>
+    <row r="278">
+      <c r="A278" t="str">
+        <v>TSK-E2E-006</v>
+      </c>
+      <c r="B278" t="str">
+        <v>manage  tasks</v>
+      </c>
+      <c r="C278" t="str">
+        <v>Tasks</v>
+      </c>
+      <c r="D278" t="str">
+        <v>Dashboard</v>
+      </c>
+      <c r="E278" t="str">
+        <v>STANDARD</v>
+      </c>
+      <c r="F278" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="G278" t="str">
+        <v>User journey completed successfully</v>
+      </c>
+      <c r="H278" t="str">
+        <v/>
+      </c>
+      <c r="I278" t="str">
+        <v/>
+      </c>
+      <c r="J278">
+        <v>1</v>
+      </c>
+      <c r="K278" t="str">
+        <v>2026-07-10T04:31:17.085Z</v>
+      </c>
+      <c r="L278" t="str">
+        <v>Local Dev</v>
+      </c>
+      <c r="M278" t="str">
+        <v>local</v>
+      </c>
+    </row>
+    <row r="279">
+      <c r="A279" t="str">
+        <v>TSK-E2E-007</v>
+      </c>
+      <c r="B279" t="str">
+        <v>manage tasks</v>
+      </c>
+      <c r="C279" t="str">
+        <v>Tasks</v>
+      </c>
+      <c r="D279" t="str">
+        <v>Dashboard</v>
+      </c>
+      <c r="E279" t="str">
+        <v>STANDARD</v>
+      </c>
+      <c r="F279" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="G279" t="str">
+        <v>User journey completed successfully</v>
+      </c>
+      <c r="H279" t="str">
+        <v/>
+      </c>
+      <c r="I279" t="str">
+        <v/>
+      </c>
+      <c r="J279">
+        <v>1</v>
+      </c>
+      <c r="K279" t="str">
+        <v>2026-07-10T04:31:17.085Z</v>
+      </c>
+      <c r="L279" t="str">
+        <v>Local Dev</v>
+      </c>
+      <c r="M279" t="str">
+        <v>local</v>
+      </c>
+    </row>
+    <row r="280">
+      <c r="A280" t="str">
+        <v>TSK-E2E-008</v>
+      </c>
+      <c r="B280" t="str">
+        <v>manage tasks</v>
+      </c>
+      <c r="C280" t="str">
+        <v>Tasks</v>
+      </c>
+      <c r="D280" t="str">
+        <v>Dashboard</v>
+      </c>
+      <c r="E280" t="str">
+        <v>STANDARD</v>
+      </c>
+      <c r="F280" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="G280" t="str">
+        <v>User journey completed successfully</v>
+      </c>
+      <c r="H280" t="str">
+        <v/>
+      </c>
+      <c r="I280" t="str">
+        <v/>
+      </c>
+      <c r="J280">
+        <v>2</v>
+      </c>
+      <c r="K280" t="str">
+        <v>2026-07-10T04:31:17.085Z</v>
+      </c>
+      <c r="L280" t="str">
+        <v>Local Dev</v>
+      </c>
+      <c r="M280" t="str">
+        <v>local</v>
+      </c>
+    </row>
+    <row r="281">
+      <c r="A281" t="str">
+        <v>DOC-E2E-007</v>
+      </c>
+      <c r="B281" t="str">
+        <v>Add Documents</v>
+      </c>
+      <c r="C281" t="str">
+        <v>Documents</v>
+      </c>
+      <c r="D281" t="str">
+        <v>Document List</v>
+      </c>
+      <c r="E281" t="str">
+        <v>STANDARD</v>
+      </c>
+      <c r="F281" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="G281" t="str">
+        <v>User journey completed successfully</v>
+      </c>
+      <c r="H281" t="str">
+        <v/>
+      </c>
+      <c r="I281" t="str">
+        <v/>
+      </c>
+      <c r="J281">
+        <v>1</v>
+      </c>
+      <c r="K281" t="str">
+        <v>2026-07-10T04:31:17.085Z</v>
+      </c>
+      <c r="L281" t="str">
+        <v>Local Dev</v>
+      </c>
+      <c r="M281" t="str">
+        <v>local</v>
+      </c>
+    </row>
+    <row r="282">
+      <c r="A282" t="str">
+        <v>DOC-E2E-008</v>
+      </c>
+      <c r="B282" t="str">
+        <v>Add Equipment Register</v>
+      </c>
+      <c r="C282" t="str">
+        <v>Documents</v>
+      </c>
+      <c r="D282" t="str">
+        <v>Document List</v>
+      </c>
+      <c r="E282" t="str">
+        <v>STANDARD</v>
+      </c>
+      <c r="F282" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="G282" t="str">
+        <v>User journey completed successfully</v>
+      </c>
+      <c r="H282" t="str">
+        <v/>
+      </c>
+      <c r="I282" t="str">
+        <v/>
+      </c>
+      <c r="J282">
+        <v>2</v>
+      </c>
+      <c r="K282" t="str">
+        <v>2026-07-10T04:31:17.085Z</v>
+      </c>
+      <c r="L282" t="str">
+        <v>Local Dev</v>
+      </c>
+      <c r="M282" t="str">
+        <v>local</v>
+      </c>
+    </row>
+    <row r="283">
+      <c r="A283" t="str">
+        <v>DOC-E2E-009</v>
+      </c>
+      <c r="B283" t="str">
+        <v>Real-time compliance monitoring of document expirations and equipment warranties.</v>
+      </c>
+      <c r="C283" t="str">
+        <v>Documents</v>
+      </c>
+      <c r="D283" t="str">
+        <v>Expiry Tracker</v>
+      </c>
+      <c r="E283" t="str">
+        <v>STANDARD</v>
+      </c>
+      <c r="F283" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="G283" t="str">
+        <v>User journey completed successfully</v>
+      </c>
+      <c r="H283" t="str">
+        <v/>
+      </c>
+      <c r="I283" t="str">
+        <v/>
+      </c>
+      <c r="J283">
+        <v>2</v>
+      </c>
+      <c r="K283" t="str">
+        <v>2026-07-10T04:31:17.085Z</v>
+      </c>
+      <c r="L283" t="str">
+        <v>Local Dev</v>
+      </c>
+      <c r="M283" t="str">
+        <v>local</v>
+      </c>
+    </row>
+    <row r="284">
+      <c r="A284" t="str">
+        <v>DOC-E2E-010</v>
+      </c>
+      <c r="B284" t="str">
+        <v>Weekly completion rates, task analytics, and full security system audit trials.</v>
+      </c>
+      <c r="C284" t="str">
+        <v>Documents</v>
+      </c>
+      <c r="D284" t="str">
+        <v>Reports</v>
+      </c>
+      <c r="E284" t="str">
+        <v>STANDARD</v>
+      </c>
+      <c r="F284" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="G284" t="str">
+        <v>User journey completed successfully</v>
+      </c>
+      <c r="H284" t="str">
+        <v/>
+      </c>
+      <c r="I284" t="str">
+        <v/>
+      </c>
+      <c r="J284">
+        <v>2</v>
+      </c>
+      <c r="K284" t="str">
+        <v>2026-07-10T04:31:17.085Z</v>
+      </c>
+      <c r="L284" t="str">
+        <v>Local Dev</v>
+      </c>
+      <c r="M284" t="str">
+        <v>local</v>
+      </c>
+    </row>
+    <row r="285">
+      <c r="A285" t="str">
+        <v>BIL-E2E-029</v>
+      </c>
+      <c r="B285" t="str">
+        <v>Track and follow up on outstanding patient balances</v>
+      </c>
+      <c r="C285" t="str">
+        <v>Billing</v>
+      </c>
+      <c r="D285" t="str">
+        <v>Balance Reminders</v>
+      </c>
+      <c r="E285" t="str">
+        <v>ACCOUNTANT</v>
+      </c>
+      <c r="F285" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="G285" t="str">
+        <v>User journey completed successfully</v>
+      </c>
+      <c r="H285" t="str">
+        <v/>
+      </c>
+      <c r="I285" t="str">
+        <v/>
+      </c>
+      <c r="J285">
+        <v>1</v>
+      </c>
+      <c r="K285" t="str">
+        <v>2026-07-10T04:31:17.085Z</v>
+      </c>
+      <c r="L285" t="str">
+        <v>Local Dev</v>
+      </c>
+      <c r="M285" t="str">
+        <v>local</v>
+      </c>
+    </row>
+    <row r="286">
+      <c r="A286" t="str">
+        <v>BIL-E2E-030</v>
+      </c>
+      <c r="B286" t="str">
+        <v>Manage log contacts</v>
+      </c>
+      <c r="C286" t="str">
+        <v>Billing</v>
+      </c>
+      <c r="D286" t="str">
+        <v>Balance Reminders</v>
+      </c>
+      <c r="E286" t="str">
+        <v>ACCOUNTANT</v>
+      </c>
+      <c r="F286" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="G286" t="str">
+        <v>User journey completed successfully</v>
+      </c>
+      <c r="H286" t="str">
+        <v/>
+      </c>
+      <c r="I286" t="str">
+        <v/>
+      </c>
+      <c r="J286">
+        <v>1</v>
+      </c>
+      <c r="K286" t="str">
+        <v>2026-07-10T04:31:17.085Z</v>
+      </c>
+      <c r="L286" t="str">
+        <v>Local Dev</v>
+      </c>
+      <c r="M286" t="str">
+        <v>local</v>
+      </c>
+    </row>
+    <row r="287">
+      <c r="A287" t="str">
+        <v>BIL-E2E-031</v>
+      </c>
+      <c r="B287" t="str">
+        <v>Schedule follow up</v>
+      </c>
+      <c r="C287" t="str">
+        <v>Billing</v>
+      </c>
+      <c r="D287" t="str">
+        <v>Balance Reminders</v>
+      </c>
+      <c r="E287" t="str">
+        <v>ACCOUNTANT</v>
+      </c>
+      <c r="F287" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="G287" t="str">
+        <v>User journey completed successfully</v>
+      </c>
+      <c r="H287" t="str">
+        <v/>
+      </c>
+      <c r="I287" t="str">
+        <v/>
+      </c>
+      <c r="J287">
+        <v>1</v>
+      </c>
+      <c r="K287" t="str">
+        <v>2026-07-10T04:31:17.085Z</v>
+      </c>
+      <c r="L287" t="str">
+        <v>Local Dev</v>
+      </c>
+      <c r="M287" t="str">
+        <v>local</v>
+      </c>
+    </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:M142"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:M287"/>
   </ignoredErrors>
 </worksheet>
 </file>